--- a/data/processed/index.xlsx
+++ b/data/processed/index.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F343"/>
+  <dimension ref="A1:D346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,20 +462,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>unstandardized</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>unstandardized weighted</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>standardized</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>standardized weighted</t>
         </is>
@@ -492,12 +482,6 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -507,16 +491,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.76080833764982</v>
+        <v>33.38628184599128</v>
       </c>
       <c r="D3" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E3" t="n">
-        <v>34.70901502600083</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5.522215552049443</v>
+        <v>5.31933553817221</v>
       </c>
     </row>
     <row r="4">
@@ -525,16 +503,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.475513159640891</v>
+        <v>17.76582580136102</v>
       </c>
       <c r="D4" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E4" t="n">
-        <v>17.9555146102165</v>
-      </c>
-      <c r="F4" t="n">
-        <v>52.40874969493209</v>
+        <v>51.92895786955497</v>
       </c>
     </row>
     <row r="5">
@@ -543,16 +515,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.35839275706735</v>
+        <v>62.2660357804046</v>
       </c>
       <c r="D5" t="n">
-        <v>48.15121544176888</v>
-      </c>
-      <c r="E5" t="n">
-        <v>63.6429829558917</v>
-      </c>
-      <c r="F5" t="n">
-        <v>110.3397149419136</v>
+        <v>109.1772512772822</v>
       </c>
     </row>
     <row r="6">
@@ -566,12 +532,6 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -579,16 +539,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>3.879587750017599</v>
+        <v>19.83133913813993</v>
       </c>
       <c r="D7" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E7" t="n">
-        <v>20.04308179177074</v>
-      </c>
-      <c r="F7" t="n">
-        <v>52.40874969493209</v>
+        <v>51.92895786955498</v>
       </c>
     </row>
     <row r="8">
@@ -602,12 +556,6 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -615,16 +563,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>58.94040358360069</v>
+        <v>30.86223304663799</v>
       </c>
       <c r="D9" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E9" t="n">
-        <v>32.08496578004888</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5.522215552049443</v>
+        <v>5.31933553817221</v>
       </c>
     </row>
     <row r="10">
@@ -633,16 +575,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>78.65449713860056</v>
+        <v>69.4465928652026</v>
       </c>
       <c r="D10" t="n">
-        <v>48.15121544176888</v>
-      </c>
-      <c r="E10" t="n">
-        <v>71.02926578561306</v>
-      </c>
-      <c r="F10" t="n">
-        <v>69.10698154182671</v>
+        <v>68.32199546516428</v>
       </c>
     </row>
     <row r="11">
@@ -656,12 +592,6 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -674,12 +604,6 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -687,16 +611,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>62.49147137714683</v>
+        <v>49.01427245237642</v>
       </c>
       <c r="D13" t="n">
-        <v>32.10081029451258</v>
-      </c>
-      <c r="E13" t="n">
-        <v>50.43081766440054</v>
-      </c>
-      <c r="F13" t="n">
-        <v>57.93096524698154</v>
+        <v>57.24829340772719</v>
       </c>
     </row>
     <row r="14">
@@ -707,16 +625,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57.5558974591537</v>
+        <v>30.13728126366327</v>
       </c>
       <c r="D14" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E14" t="n">
-        <v>31.33129208722894</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5.522215552049442</v>
+        <v>5.31933553817221</v>
       </c>
     </row>
     <row r="15">
@@ -730,12 +642,6 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
@@ -748,12 +654,6 @@
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -761,16 +661,10 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>54.55534584153601</v>
+        <v>38.43950867634653</v>
       </c>
       <c r="D17" t="n">
-        <v>32.10081029451258</v>
-      </c>
-      <c r="E17" t="n">
-        <v>39.41254111242045</v>
-      </c>
-      <c r="F17" t="n">
-        <v>16.69823184689461</v>
+        <v>16.39303759560929</v>
       </c>
     </row>
     <row r="18">
@@ -784,12 +678,6 @@
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -797,16 +685,10 @@
         <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>3.295860384863144</v>
+        <v>16.84749237696323</v>
       </c>
       <c r="D19" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.02737598028794</v>
-      </c>
-      <c r="F19" t="n">
-        <v>52.40874969493209</v>
+        <v>51.92895786955498</v>
       </c>
     </row>
     <row r="20">
@@ -820,12 +702,6 @@
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -833,16 +709,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>6.576555767955446</v>
+        <v>33.61746561722263</v>
       </c>
       <c r="D21" t="n">
-        <v>32.10081029451258</v>
-      </c>
-      <c r="E21" t="n">
-        <v>33.9764051385807</v>
-      </c>
-      <c r="F21" t="n">
-        <v>104.8174993898642</v>
+        <v>103.85791573911</v>
       </c>
     </row>
     <row r="22">
@@ -851,16 +721,10 @@
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>30.15768446257602</v>
+        <v>58.48746191995887</v>
       </c>
       <c r="D22" t="n">
-        <v>48.15121544176888</v>
-      </c>
-      <c r="E22" t="n">
-        <v>59.11194271295007</v>
-      </c>
-      <c r="F22" t="n">
-        <v>115.9935156847093</v>
+        <v>114.931617796547</v>
       </c>
     </row>
     <row r="23">
@@ -874,12 +738,6 @@
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -892,12 +750,6 @@
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -910,12 +762,6 @@
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -928,12 +774,6 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -943,16 +783,10 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>19.07859559825117</v>
+        <v>20.79677973320532</v>
       </c>
       <c r="D27" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E27" t="n">
-        <v>21.01883056381289</v>
-      </c>
-      <c r="F27" t="n">
-        <v>11.17601629484516</v>
+        <v>11.07370205743708</v>
       </c>
     </row>
     <row r="28">
@@ -961,16 +795,10 @@
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>3.701264014421192</v>
+        <v>18.9197993806035</v>
       </c>
       <c r="D28" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E28" t="n">
-        <v>19.12180936586501</v>
-      </c>
-      <c r="F28" t="n">
-        <v>52.40874969493209</v>
+        <v>51.92895786955497</v>
       </c>
     </row>
     <row r="29">
@@ -984,12 +812,6 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -997,16 +819,10 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>4.081784255789577</v>
+        <v>20.86490964533951</v>
       </c>
       <c r="D30" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E30" t="n">
-        <v>21.08768791085637</v>
-      </c>
-      <c r="F30" t="n">
-        <v>52.40874969493209</v>
+        <v>51.92895786955498</v>
       </c>
     </row>
     <row r="31">
@@ -1015,16 +831,10 @@
         <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>3.717307638237495</v>
+        <v>19.00180978103958</v>
       </c>
       <c r="D31" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E31" t="n">
-        <v>19.20469540559568</v>
-      </c>
-      <c r="F31" t="n">
-        <v>52.40874969493209</v>
+        <v>51.92895786955497</v>
       </c>
     </row>
     <row r="32">
@@ -1038,12 +848,6 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1056,12 +860,6 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
@@ -1074,12 +872,6 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
@@ -1092,12 +884,6 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
@@ -1110,12 +896,6 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
@@ -1123,16 +903,10 @@
         <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>6.291300299982687</v>
+        <v>32.15932153313769</v>
       </c>
       <c r="D37" t="n">
-        <v>21.40054019634172</v>
-      </c>
-      <c r="E37" t="n">
-        <v>32.50269219676055</v>
-      </c>
-      <c r="F37" t="n">
-        <v>69.87833292657611</v>
+        <v>69.23861049273997</v>
       </c>
     </row>
     <row r="38">
@@ -1146,12 +920,6 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1161,16 +929,10 @@
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>16.9315473275694</v>
+        <v>18.45637214230166</v>
       </c>
       <c r="D39" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E39" t="n">
-        <v>18.65343403442033</v>
-      </c>
-      <c r="F39" t="n">
-        <v>11.17601629484516</v>
+        <v>11.07370205743708</v>
       </c>
     </row>
     <row r="40">
@@ -1184,12 +946,6 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
@@ -1197,16 +953,10 @@
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>6.825172082303145</v>
+        <v>34.88832086339699</v>
       </c>
       <c r="D41" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E41" t="n">
-        <v>35.26082952702684</v>
-      </c>
-      <c r="F41" t="n">
-        <v>52.40874969493209</v>
+        <v>51.92895786955498</v>
       </c>
     </row>
     <row r="42">
@@ -1220,12 +970,6 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n"/>
@@ -1233,16 +977,10 @@
         <v>6</v>
       </c>
       <c r="C43" t="n">
-        <v>48.57328842402389</v>
+        <v>37.74169850513731</v>
       </c>
       <c r="D43" t="n">
-        <v>25.68064823561006</v>
-      </c>
-      <c r="E43" t="n">
-        <v>38.84012332048481</v>
-      </c>
-      <c r="F43" t="n">
-        <v>46.34477219758522</v>
+        <v>45.79863472618174</v>
       </c>
     </row>
     <row r="44">
@@ -1251,16 +989,10 @@
         <v>7</v>
       </c>
       <c r="C44" t="n">
-        <v>12.61850313333609</v>
+        <v>23.2904889328315</v>
       </c>
       <c r="D44" t="n">
-        <v>25.68064823561007</v>
-      </c>
-      <c r="E44" t="n">
-        <v>23.53916552984014</v>
-      </c>
-      <c r="F44" t="n">
-        <v>50.86781279182181</v>
+        <v>50.40212794159364</v>
       </c>
     </row>
     <row r="45">
@@ -1274,12 +1006,6 @@
       <c r="D45" t="n">
         <v>0</v>
       </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
@@ -1292,12 +1018,6 @@
       <c r="D46" t="n">
         <v>0</v>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n"/>
@@ -1305,16 +1025,10 @@
         <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>9.779989988782782</v>
+        <v>10.66075836359321</v>
       </c>
       <c r="D47" t="n">
-        <v>12.84032411780503</v>
-      </c>
-      <c r="E47" t="n">
-        <v>10.77458513292533</v>
-      </c>
-      <c r="F47" t="n">
-        <v>8.940813035876131</v>
+        <v>8.858961645949664</v>
       </c>
     </row>
     <row r="48">
@@ -1323,16 +1037,10 @@
         <v>11</v>
       </c>
       <c r="C48" t="n">
-        <v>10.27814678221891</v>
+        <v>11.20377826525938</v>
       </c>
       <c r="D48" t="n">
-        <v>12.84032411780504</v>
-      </c>
-      <c r="E48" t="n">
-        <v>11.32340295243014</v>
-      </c>
-      <c r="F48" t="n">
-        <v>8.940813035876131</v>
+        <v>8.858961645949664</v>
       </c>
     </row>
     <row r="49">
@@ -1346,12 +1054,6 @@
       <c r="D49" t="n">
         <v>0</v>
       </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -1364,12 +1066,6 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1384,12 +1080,6 @@
       <c r="D51" t="n">
         <v>0</v>
       </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n"/>
@@ -1397,16 +1087,10 @@
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>35.60090138617925</v>
+        <v>55.1523593502596</v>
       </c>
       <c r="D52" t="n">
-        <v>38.5209723534151</v>
-      </c>
-      <c r="E52" t="n">
-        <v>55.74123067364717</v>
-      </c>
-      <c r="F52" t="n">
-        <v>34.53149622197915</v>
+        <v>34.21536714617049</v>
       </c>
     </row>
     <row r="53">
@@ -1415,16 +1099,10 @@
         <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>20.0604180617869</v>
+        <v>21.86702336859834</v>
       </c>
       <c r="D53" t="n">
-        <v>25.68064823561006</v>
-      </c>
-      <c r="E53" t="n">
-        <v>22.10050137645355</v>
-      </c>
-      <c r="F53" t="n">
-        <v>17.88162607175226</v>
+        <v>17.71792329189933</v>
       </c>
     </row>
     <row r="54">
@@ -1433,16 +1111,10 @@
         <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>29.6741478249616</v>
+        <v>15.53790625704439</v>
       </c>
       <c r="D54" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E54" t="n">
-        <v>16.15350353286198</v>
-      </c>
-      <c r="F54" t="n">
-        <v>5.522215552049443</v>
+        <v>5.31933553817221</v>
       </c>
     </row>
     <row r="55">
@@ -1451,16 +1123,10 @@
         <v>6</v>
       </c>
       <c r="C55" t="n">
-        <v>61.10703233493366</v>
+        <v>51.23219186116456</v>
       </c>
       <c r="D55" t="n">
-        <v>48.15121544176888</v>
-      </c>
-      <c r="E55" t="n">
-        <v>52.47419214492866</v>
-      </c>
-      <c r="F55" t="n">
-        <v>69.10698154182668</v>
+        <v>68.32199546516426</v>
       </c>
     </row>
     <row r="56">
@@ -1474,12 +1140,6 @@
       <c r="D56" t="n">
         <v>0</v>
       </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n"/>
@@ -1487,16 +1147,10 @@
         <v>8</v>
       </c>
       <c r="C57" t="n">
-        <v>65.34060110460371</v>
+        <v>41.67252574720311</v>
       </c>
       <c r="D57" t="n">
-        <v>25.68064823561006</v>
-      </c>
-      <c r="E57" t="n">
-        <v>42.90811538434922</v>
-      </c>
-      <c r="F57" t="n">
-        <v>13.35858547751568</v>
+        <v>13.11443007648743</v>
       </c>
     </row>
     <row r="58">
@@ -1505,16 +1159,10 @@
         <v>9</v>
       </c>
       <c r="C58" t="n">
-        <v>12.43775013983162</v>
+        <v>13.55787163172704</v>
       </c>
       <c r="D58" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E58" t="n">
-        <v>13.70263138279028</v>
-      </c>
-      <c r="F58" t="n">
-        <v>11.17601629484516</v>
+        <v>11.07370205743708</v>
       </c>
     </row>
     <row r="59">
@@ -1528,12 +1176,6 @@
       <c r="D59" t="n">
         <v>0</v>
       </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n"/>
@@ -1541,16 +1183,10 @@
         <v>11</v>
       </c>
       <c r="C60" t="n">
-        <v>10.09663425626361</v>
+        <v>11.00591904644685</v>
       </c>
       <c r="D60" t="n">
-        <v>12.84032411780503</v>
-      </c>
-      <c r="E60" t="n">
-        <v>11.12343115636073</v>
-      </c>
-      <c r="F60" t="n">
-        <v>8.940813035876131</v>
+        <v>8.858961645949664</v>
       </c>
     </row>
     <row r="61">
@@ -1559,16 +1195,10 @@
         <v>12</v>
       </c>
       <c r="C61" t="n">
-        <v>11.68767117058113</v>
+        <v>12.74024189448149</v>
       </c>
       <c r="D61" t="n">
-        <v>12.84032411780503</v>
-      </c>
-      <c r="E61" t="n">
-        <v>12.87627167077873</v>
-      </c>
-      <c r="F61" t="n">
-        <v>8.940813035876131</v>
+        <v>8.858961645949664</v>
       </c>
     </row>
     <row r="62">
@@ -1579,16 +1209,10 @@
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>63.00837838211764</v>
+        <v>62.63585677517529</v>
       </c>
       <c r="D62" t="n">
-        <v>38.5209723534151</v>
-      </c>
-      <c r="E62" t="n">
-        <v>63.83780914367625</v>
-      </c>
-      <c r="F62" t="n">
-        <v>30.00845562774258</v>
+        <v>29.6118739307586</v>
       </c>
     </row>
     <row r="63">
@@ -1597,16 +1221,10 @@
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>38.76080778040181</v>
+        <v>42.25153667830867</v>
       </c>
       <c r="D63" t="n">
-        <v>38.5209723534151</v>
-      </c>
-      <c r="E63" t="n">
-        <v>42.70266367653738</v>
-      </c>
-      <c r="F63" t="n">
-        <v>26.82243910762839</v>
+        <v>26.57688493784899</v>
       </c>
     </row>
     <row r="64">
@@ -1620,12 +1238,6 @@
       <c r="D64" t="n">
         <v>0</v>
       </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n"/>
@@ -1633,16 +1245,10 @@
         <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>18.97832082193948</v>
+        <v>38.52488145664204</v>
       </c>
       <c r="D65" t="n">
-        <v>12.84032411780503</v>
-      </c>
-      <c r="E65" t="n">
-        <v>38.93621830957062</v>
-      </c>
-      <c r="F65" t="n">
-        <v>16.64987015022689</v>
+        <v>16.49744385427117</v>
       </c>
     </row>
     <row r="66">
@@ -1651,16 +1257,10 @@
         <v>5</v>
       </c>
       <c r="C66" t="n">
-        <v>17.47939612007929</v>
+        <v>35.48215196579898</v>
       </c>
       <c r="D66" t="n">
-        <v>12.84032411780503</v>
-      </c>
-      <c r="E66" t="n">
-        <v>35.86100106728606</v>
-      </c>
-      <c r="F66" t="n">
-        <v>16.64987015022689</v>
+        <v>16.49744385427116</v>
       </c>
     </row>
     <row r="67">
@@ -1674,12 +1274,6 @@
       <c r="D67" t="n">
         <v>0</v>
       </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n"/>
@@ -1687,16 +1281,10 @@
         <v>7</v>
       </c>
       <c r="C68" t="n">
-        <v>14.62827926893629</v>
+        <v>15.94567588925508</v>
       </c>
       <c r="D68" t="n">
-        <v>12.84032411780503</v>
-      </c>
-      <c r="E68" t="n">
-        <v>16.11593064125185</v>
-      </c>
-      <c r="F68" t="n">
-        <v>8.940813035876131</v>
+        <v>8.858961645949664</v>
       </c>
     </row>
     <row r="69">
@@ -1705,16 +1293,10 @@
         <v>8</v>
       </c>
       <c r="C69" t="n">
-        <v>33.10331955189925</v>
+        <v>36.08454519691499</v>
       </c>
       <c r="D69" t="n">
-        <v>25.68064823561006</v>
-      </c>
-      <c r="E69" t="n">
-        <v>36.46982615559525</v>
-      </c>
-      <c r="F69" t="n">
-        <v>17.88162607175226</v>
+        <v>17.71792329189933</v>
       </c>
     </row>
     <row r="70">
@@ -1728,12 +1310,6 @@
       <c r="D70" t="n">
         <v>0</v>
       </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n"/>
@@ -1741,16 +1317,10 @@
         <v>10</v>
       </c>
       <c r="C71" t="n">
-        <v>10.95952552257367</v>
+        <v>11.94652075409047</v>
       </c>
       <c r="D71" t="n">
-        <v>12.84032411780503</v>
-      </c>
-      <c r="E71" t="n">
-        <v>12.0740758318644</v>
-      </c>
-      <c r="F71" t="n">
-        <v>8.940813035876131</v>
+        <v>8.858961645949664</v>
       </c>
     </row>
     <row r="72">
@@ -1759,16 +1329,10 @@
         <v>11</v>
       </c>
       <c r="C72" t="n">
-        <v>35.18288706221087</v>
+        <v>18.42237911091622</v>
       </c>
       <c r="D72" t="n">
-        <v>12.84032411780503</v>
-      </c>
-      <c r="E72" t="n">
-        <v>19.15225649639841</v>
-      </c>
-      <c r="F72" t="n">
-        <v>4.417772441639554</v>
+        <v>4.255468430537769</v>
       </c>
     </row>
     <row r="73">
@@ -1777,16 +1341,10 @@
         <v>12</v>
       </c>
       <c r="C73" t="n">
-        <v>64.8718274446618</v>
+        <v>155.5218145389313</v>
       </c>
       <c r="D73" t="n">
-        <v>51.36129647122013</v>
-      </c>
-      <c r="E73" t="n">
-        <v>157.1823479743472</v>
-      </c>
-      <c r="F73" t="n">
-        <v>84.16755309227558</v>
+        <v>83.39701565013597</v>
       </c>
     </row>
     <row r="74">
@@ -1797,16 +1355,10 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>26.1625681773143</v>
+        <v>40.52658560605645</v>
       </c>
       <c r="D74" t="n">
-        <v>25.68064823561007</v>
-      </c>
-      <c r="E74" t="n">
-        <v>40.95929500198016</v>
-      </c>
-      <c r="F74" t="n">
-        <v>25.59068318610302</v>
+        <v>25.35640550022083</v>
       </c>
     </row>
     <row r="75">
@@ -1815,16 +1367,10 @@
         <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>68.30291195327989</v>
+        <v>109.0212634931692</v>
       </c>
       <c r="D75" t="n">
-        <v>51.36129647122014</v>
-      </c>
-      <c r="E75" t="n">
-        <v>110.7677663108454</v>
-      </c>
-      <c r="F75" t="n">
-        <v>79.64451249803902</v>
+        <v>78.79352243472408</v>
       </c>
     </row>
     <row r="76">
@@ -1833,16 +1379,10 @@
         <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>97.43635261518419</v>
+        <v>160.5818024311168</v>
       </c>
       <c r="D76" t="n">
-        <v>121.9830791191478</v>
-      </c>
-      <c r="E76" t="n">
-        <v>162.2963622364196</v>
-      </c>
-      <c r="F76" t="n">
-        <v>139.5407794559661</v>
+        <v>138.2633109859217</v>
       </c>
     </row>
     <row r="77">
@@ -1851,16 +1391,10 @@
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>69.0091833407992</v>
+        <v>75.22402674327545</v>
       </c>
       <c r="D77" t="n">
-        <v>77.04194470683019</v>
-      </c>
-      <c r="E77" t="n">
-        <v>76.02720674682764</v>
-      </c>
-      <c r="F77" t="n">
-        <v>53.64487821525679</v>
+        <v>53.15376987569798</v>
       </c>
     </row>
     <row r="78">
@@ -1869,16 +1403,10 @@
         <v>5</v>
       </c>
       <c r="C78" t="n">
-        <v>12.03625083707214</v>
+        <v>13.120214021159</v>
       </c>
       <c r="D78" t="n">
-        <v>12.84032411780504</v>
-      </c>
-      <c r="E78" t="n">
-        <v>13.26030082587213</v>
-      </c>
-      <c r="F78" t="n">
-        <v>8.940813035876131</v>
+        <v>8.858961645949664</v>
       </c>
     </row>
     <row r="79">
@@ -1887,16 +1415,10 @@
         <v>6</v>
       </c>
       <c r="C79" t="n">
-        <v>102.9703238400304</v>
+        <v>109.9776746425472</v>
       </c>
       <c r="D79" t="n">
-        <v>89.88226882463523</v>
-      </c>
-      <c r="E79" t="n">
-        <v>111.7169786241728</v>
-      </c>
-      <c r="F79" t="n">
-        <v>73.48076488559788</v>
+        <v>72.68620272287876</v>
       </c>
     </row>
     <row r="80">
@@ -1905,16 +1427,10 @@
         <v>7</v>
       </c>
       <c r="C80" t="n">
-        <v>4.261281352255355</v>
+        <v>21.78244728688612</v>
       </c>
       <c r="D80" t="n">
-        <v>12.84032411780504</v>
-      </c>
-      <c r="E80" t="n">
-        <v>22.01502226122198</v>
-      </c>
-      <c r="F80" t="n">
-        <v>41.92699975594567</v>
+        <v>41.54316629564398</v>
       </c>
     </row>
     <row r="81">
@@ -1923,16 +1439,10 @@
         <v>8</v>
       </c>
       <c r="C81" t="n">
-        <v>21.01220492373007</v>
+        <v>45.82082058600466</v>
       </c>
       <c r="D81" t="n">
-        <v>25.68064823561007</v>
-      </c>
-      <c r="E81" t="n">
-        <v>46.31005744867131</v>
-      </c>
-      <c r="F81" t="n">
-        <v>50.86781279182181</v>
+        <v>50.40212794159364</v>
       </c>
     </row>
     <row r="82">
@@ -1941,16 +1451,10 @@
         <v>9</v>
       </c>
       <c r="C82" t="n">
-        <v>19.38439366213215</v>
+        <v>29.71058669028257</v>
       </c>
       <c r="D82" t="n">
-        <v>25.68064823561007</v>
-      </c>
-      <c r="E82" t="n">
-        <v>30.02781178652581</v>
-      </c>
-      <c r="F82" t="n">
-        <v>25.59068318610302</v>
+        <v>25.35640550022083</v>
       </c>
     </row>
     <row r="83">
@@ -1959,16 +1463,10 @@
         <v>10</v>
       </c>
       <c r="C83" t="n">
-        <v>78.46325171603061</v>
+        <v>77.53421863565208</v>
       </c>
       <c r="D83" t="n">
-        <v>77.04194470683019</v>
-      </c>
-      <c r="E83" t="n">
-        <v>78.79799701963491</v>
-      </c>
-      <c r="F83" t="n">
-        <v>56.83089473537096</v>
+        <v>56.18875886860758</v>
       </c>
     </row>
     <row r="84">
@@ -1977,16 +1475,10 @@
         <v>11</v>
       </c>
       <c r="C84" t="n">
-        <v>153.3610257208995</v>
+        <v>157.8118925162792</v>
       </c>
       <c r="D84" t="n">
-        <v>128.4032411780503</v>
-      </c>
-      <c r="E84" t="n">
-        <v>160.5855664792637</v>
-      </c>
-      <c r="F84" t="n">
-        <v>121.0572930047085</v>
+        <v>119.7053168866887</v>
       </c>
     </row>
     <row r="85">
@@ -1995,16 +1487,10 @@
         <v>12</v>
       </c>
       <c r="C85" t="n">
-        <v>65.79428114209715</v>
+        <v>43.70274203408804</v>
       </c>
       <c r="D85" t="n">
-        <v>32.10081029451258</v>
-      </c>
-      <c r="E85" t="n">
-        <v>44.81313963289156</v>
-      </c>
-      <c r="F85" t="n">
-        <v>16.31868954747481</v>
+        <v>16.04743497420339</v>
       </c>
     </row>
     <row r="86">
@@ -2015,16 +1501,10 @@
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>57.10861235099019</v>
+        <v>62.47830593891357</v>
       </c>
       <c r="D86" t="n">
-        <v>51.36129647122013</v>
-      </c>
-      <c r="E86" t="n">
-        <v>63.57950955148386</v>
-      </c>
-      <c r="F86" t="n">
-        <v>64.22639826933748</v>
+        <v>63.51655801808108</v>
       </c>
     </row>
     <row r="87">
@@ -2033,16 +1513,10 @@
         <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>96.98230226144889</v>
+        <v>103.9558492390404</v>
       </c>
       <c r="D87" t="n">
-        <v>64.20162058902517</v>
-      </c>
-      <c r="E87" t="n">
-        <v>106.1376574741825</v>
-      </c>
-      <c r="F87" t="n">
-        <v>84.06228493967858</v>
+        <v>83.04899086526186</v>
       </c>
     </row>
     <row r="88">
@@ -2051,16 +1525,10 @@
         <v>3</v>
       </c>
       <c r="C88" t="n">
-        <v>43.11859464818418</v>
+        <v>73.5477775816492</v>
       </c>
       <c r="D88" t="n">
-        <v>51.36129647122014</v>
-      </c>
-      <c r="E88" t="n">
-        <v>74.33305998165801</v>
-      </c>
-      <c r="F88" t="n">
-        <v>76.45849597792483</v>
+        <v>75.75853344181446</v>
       </c>
     </row>
     <row r="89">
@@ -2069,16 +1537,10 @@
         <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>68.1509459088727</v>
+        <v>64.9994892373105</v>
       </c>
       <c r="D89" t="n">
-        <v>51.36129647122014</v>
-      </c>
-      <c r="E89" t="n">
-        <v>66.18162118708585</v>
-      </c>
-      <c r="F89" t="n">
-        <v>38.94926866361871</v>
+        <v>38.47083557670826</v>
       </c>
     </row>
     <row r="90">
@@ -2087,16 +1549,10 @@
         <v>5</v>
       </c>
       <c r="C90" t="n">
-        <v>12.27735005818672</v>
+        <v>37.75179021652866</v>
       </c>
       <c r="D90" t="n">
-        <v>25.68064823561007</v>
-      </c>
-      <c r="E90" t="n">
-        <v>38.15487263996359</v>
-      </c>
-      <c r="F90" t="n">
-        <v>58.57686990617256</v>
+        <v>58.04061014991513</v>
       </c>
     </row>
     <row r="91">
@@ -2105,16 +1561,10 @@
         <v>6</v>
       </c>
       <c r="C91" t="n">
-        <v>44.3019227872594</v>
+        <v>66.09215119125102</v>
       </c>
       <c r="D91" t="n">
-        <v>51.36129647122014</v>
-      </c>
-      <c r="E91" t="n">
-        <v>66.79782857289035</v>
-      </c>
-      <c r="F91" t="n">
-        <v>51.18136637220605</v>
+        <v>50.71281100044166</v>
       </c>
     </row>
     <row r="92">
@@ -2123,16 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C92" t="n">
-        <v>119.1716397861599</v>
+        <v>206.0067942468064</v>
       </c>
       <c r="D92" t="n">
-        <v>141.2435652958554</v>
-      </c>
-      <c r="E92" t="n">
-        <v>208.6623724609877</v>
-      </c>
-      <c r="F92" t="n">
-        <v>271.1543457334922</v>
+        <v>268.5501207046312</v>
       </c>
     </row>
     <row r="93">
@@ -2141,16 +1585,10 @@
         <v>8</v>
       </c>
       <c r="C93" t="n">
-        <v>76.88621068907534</v>
+        <v>61.67944057384396</v>
       </c>
       <c r="D93" t="n">
-        <v>25.68064823561006</v>
-      </c>
-      <c r="E93" t="n">
-        <v>63.43242158656261</v>
-      </c>
-      <c r="F93" t="n">
-        <v>46.34477219758522</v>
+        <v>45.79863472618175</v>
       </c>
     </row>
     <row r="94">
@@ -2159,16 +1597,10 @@
         <v>9</v>
       </c>
       <c r="C94" t="n">
-        <v>12.63728352359923</v>
+        <v>37.12188904411515</v>
       </c>
       <c r="D94" t="n">
-        <v>25.68064823561006</v>
-      </c>
-      <c r="E94" t="n">
-        <v>37.51824590328824</v>
-      </c>
-      <c r="F94" t="n">
-        <v>58.57686990617258</v>
+        <v>58.04061014991513</v>
       </c>
     </row>
     <row r="95">
@@ -2177,16 +1609,10 @@
         <v>10</v>
       </c>
       <c r="C95" t="n">
-        <v>59.87938114611893</v>
+        <v>89.26103527665056</v>
       </c>
       <c r="D95" t="n">
-        <v>64.20162058902517</v>
-      </c>
-      <c r="E95" t="n">
-        <v>90.21409085921393</v>
-      </c>
-      <c r="F95" t="n">
-        <v>85.39930901380097</v>
+        <v>84.61749508776413</v>
       </c>
     </row>
     <row r="96">
@@ -2195,16 +1621,10 @@
         <v>11</v>
       </c>
       <c r="C96" t="n">
-        <v>34.81883786109773</v>
+        <v>109.2006309770866</v>
       </c>
       <c r="D96" t="n">
-        <v>70.62178264792769</v>
-      </c>
-      <c r="E96" t="n">
-        <v>110.3665850874057</v>
-      </c>
-      <c r="F96" t="n">
-        <v>187.3179732439687</v>
+        <v>185.6031139345631</v>
       </c>
     </row>
     <row r="97">
@@ -2213,16 +1633,10 @@
         <v>12</v>
       </c>
       <c r="C97" t="n">
-        <v>57.83977840826745</v>
+        <v>63.4748932223313</v>
       </c>
       <c r="D97" t="n">
-        <v>44.94113441231762</v>
-      </c>
-      <c r="E97" t="n">
-        <v>64.53985025333796</v>
-      </c>
-      <c r="F97" t="n">
-        <v>40.67761681205246</v>
+        <v>40.18336103679605</v>
       </c>
     </row>
     <row r="98">
@@ -2233,16 +1647,10 @@
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>32.66181783843402</v>
+        <v>68.85572992135165</v>
       </c>
       <c r="D98" t="n">
-        <v>51.36129647122014</v>
-      </c>
-      <c r="E98" t="n">
-        <v>69.5909145132582</v>
-      </c>
-      <c r="F98" t="n">
-        <v>101.7356255836436</v>
+        <v>100.8042558831873</v>
       </c>
     </row>
     <row r="99">
@@ -2251,16 +1659,10 @@
         <v>2</v>
       </c>
       <c r="C99" t="n">
-        <v>91.22401335036015</v>
+        <v>108.4217401685716</v>
       </c>
       <c r="D99" t="n">
-        <v>77.04194470683019</v>
-      </c>
-      <c r="E99" t="n">
-        <v>110.0162258102583</v>
-      </c>
-      <c r="F99" t="n">
-        <v>89.8170814554405</v>
+        <v>88.87296351830189</v>
       </c>
     </row>
     <row r="100">
@@ -2269,16 +1671,10 @@
         <v>3</v>
       </c>
       <c r="C100" t="n">
-        <v>80.46583928052195</v>
+        <v>131.9421683690651</v>
       </c>
       <c r="D100" t="n">
-        <v>102.7225929424403</v>
-      </c>
-      <c r="E100" t="n">
-        <v>133.3509378254121</v>
-      </c>
-      <c r="F100" t="n">
-        <v>152.9169919558497</v>
+        <v>151.517066883629</v>
       </c>
     </row>
     <row r="101">
@@ -2287,16 +1683,10 @@
         <v>4</v>
       </c>
       <c r="C101" t="n">
-        <v>41.98593865435675</v>
+        <v>82.62266249392715</v>
       </c>
       <c r="D101" t="n">
-        <v>51.36129647122014</v>
-      </c>
-      <c r="E101" t="n">
-        <v>83.50483901688627</v>
-      </c>
-      <c r="F101" t="n">
-        <v>84.16755309227558</v>
+        <v>83.39701565013597</v>
       </c>
     </row>
     <row r="102">
@@ -2305,16 +1695,10 @@
         <v>5</v>
       </c>
       <c r="C102" t="n">
-        <v>125.2013050469807</v>
+        <v>176.3284231195528</v>
       </c>
       <c r="D102" t="n">
-        <v>141.2435652958554</v>
-      </c>
-      <c r="E102" t="n">
-        <v>178.5702480686058</v>
-      </c>
-      <c r="F102" t="n">
-        <v>170.0458273106171</v>
+        <v>168.36723093914</v>
       </c>
     </row>
     <row r="103">
@@ -2323,16 +1707,10 @@
         <v>6</v>
       </c>
       <c r="C103" t="n">
-        <v>94.31524591900899</v>
+        <v>151.3952021410863</v>
       </c>
       <c r="D103" t="n">
-        <v>115.5629170602453</v>
-      </c>
-      <c r="E103" t="n">
-        <v>153.3925167638444</v>
-      </c>
-      <c r="F103" t="n">
-        <v>198.0300082319095</v>
+        <v>196.0952221721825</v>
       </c>
     </row>
     <row r="104">
@@ -2341,16 +1719,10 @@
         <v>7</v>
       </c>
       <c r="C104" t="n">
-        <v>103.438317962067</v>
+        <v>174.0606913007652</v>
       </c>
       <c r="D104" t="n">
-        <v>121.9830791191478</v>
-      </c>
-      <c r="E104" t="n">
-        <v>175.9191675444575</v>
-      </c>
-      <c r="F104" t="n">
-        <v>187.9450804047372</v>
+        <v>186.224480052259</v>
       </c>
     </row>
     <row r="105">
@@ -2359,16 +1731,10 @@
         <v>8</v>
       </c>
       <c r="C105" t="n">
-        <v>33.41831794661611</v>
+        <v>48.56003342802504</v>
       </c>
       <c r="D105" t="n">
-        <v>25.68064823561007</v>
-      </c>
-      <c r="E105" t="n">
-        <v>49.07851734213834</v>
-      </c>
-      <c r="F105" t="n">
-        <v>25.59068318610302</v>
+        <v>25.35640550022083</v>
       </c>
     </row>
     <row r="106">
@@ -2377,16 +1743,10 @@
         <v>9</v>
       </c>
       <c r="C106" t="n">
-        <v>41.10270250593619</v>
+        <v>48.4146083296199</v>
       </c>
       <c r="D106" t="n">
-        <v>38.5209723534151</v>
-      </c>
-      <c r="E106" t="n">
-        <v>48.93153951469022</v>
-      </c>
-      <c r="F106" t="n">
-        <v>56.78802093174004</v>
+        <v>56.26813773702555</v>
       </c>
     </row>
     <row r="107">
@@ -2395,16 +1755,10 @@
         <v>10</v>
       </c>
       <c r="C107" t="n">
-        <v>49.94050909724576</v>
+        <v>90.19188868904551</v>
       </c>
       <c r="D107" t="n">
-        <v>77.04194470683019</v>
-      </c>
-      <c r="E107" t="n">
-        <v>91.1548831552268</v>
-      </c>
-      <c r="F107" t="n">
-        <v>135.0353658840974</v>
+        <v>133.7991435917296</v>
       </c>
     </row>
     <row r="108">
@@ -2413,16 +1767,10 @@
         <v>11</v>
       </c>
       <c r="C108" t="n">
-        <v>85.80290745007794</v>
+        <v>94.44780673539913</v>
       </c>
       <c r="D108" t="n">
-        <v>77.04194470683019</v>
-      </c>
-      <c r="E108" t="n">
-        <v>95.92143162347143</v>
-      </c>
-      <c r="F108" t="n">
-        <v>89.8170814554405</v>
+        <v>88.87296351830192</v>
       </c>
     </row>
     <row r="109">
@@ -2431,16 +1779,10 @@
         <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>37.88346029726051</v>
+        <v>43.03403735820445</v>
       </c>
       <c r="D109" t="n">
-        <v>25.68064823561006</v>
-      </c>
-      <c r="E109" t="n">
-        <v>43.49351925215024</v>
-      </c>
-      <c r="F109" t="n">
-        <v>22.57007829014513</v>
+        <v>22.36345364970308</v>
       </c>
     </row>
     <row r="110">
@@ -2451,16 +1793,10 @@
         <v>1</v>
       </c>
       <c r="C110" t="n">
-        <v>134.3245277739411</v>
+        <v>200.632118035665</v>
       </c>
       <c r="D110" t="n">
-        <v>166.9242135314654</v>
-      </c>
-      <c r="E110" t="n">
-        <v>202.7743020193345</v>
-      </c>
-      <c r="F110" t="n">
-        <v>315.8155371092419</v>
+        <v>312.9243078027974</v>
       </c>
     </row>
     <row r="111">
@@ -2469,16 +1805,10 @@
         <v>2</v>
       </c>
       <c r="C111" t="n">
-        <v>21.88129630548954</v>
+        <v>35.20863418077622</v>
       </c>
       <c r="D111" t="n">
-        <v>25.68064823561007</v>
-      </c>
-      <c r="E111" t="n">
-        <v>35.58456288534949</v>
-      </c>
-      <c r="F111" t="n">
-        <v>50.86781279182181</v>
+        <v>50.40212794159364</v>
       </c>
     </row>
     <row r="112">
@@ -2487,16 +1817,10 @@
         <v>3</v>
       </c>
       <c r="C112" t="n">
-        <v>141.4043879048627</v>
+        <v>198.3801978728922</v>
       </c>
       <c r="D112" t="n">
-        <v>160.5040514725629</v>
-      </c>
-      <c r="E112" t="n">
-        <v>200.8892016098034</v>
-      </c>
-      <c r="F112" t="n">
-        <v>240.2100607422407</v>
+        <v>237.8891245738727</v>
       </c>
     </row>
     <row r="113">
@@ -2505,16 +1829,10 @@
         <v>4</v>
       </c>
       <c r="C113" t="n">
-        <v>107.7366505463505</v>
+        <v>106.9229667603619</v>
       </c>
       <c r="D113" t="n">
-        <v>77.04194470683019</v>
-      </c>
-      <c r="E113" t="n">
-        <v>109.4192571812508</v>
-      </c>
-      <c r="F113" t="n">
-        <v>151.266414301343</v>
+        <v>149.6378796022786</v>
       </c>
     </row>
     <row r="114">
@@ -2523,16 +1841,10 @@
         <v>5</v>
       </c>
       <c r="C114" t="n">
-        <v>111.6444554024038</v>
+        <v>208.5482783830088</v>
       </c>
       <c r="D114" t="n">
-        <v>154.0838894136604</v>
-      </c>
-      <c r="E114" t="n">
-        <v>211.375966067966</v>
-      </c>
-      <c r="F114" t="n">
-        <v>313.9519921227292</v>
+        <v>310.9559630343846</v>
       </c>
     </row>
     <row r="115">
@@ -2541,16 +1853,10 @@
         <v>6</v>
       </c>
       <c r="C115" t="n">
-        <v>27.86403459184612</v>
+        <v>65.05693511302016</v>
       </c>
       <c r="D115" t="n">
-        <v>38.5209723534151</v>
-      </c>
-      <c r="E115" t="n">
-        <v>65.75155931272565</v>
-      </c>
-      <c r="F115" t="n">
-        <v>75.22674005639945</v>
+        <v>74.53805400418631</v>
       </c>
     </row>
     <row r="116">
@@ -2559,16 +1865,10 @@
         <v>7</v>
       </c>
       <c r="C116" t="n">
-        <v>118.3552043686345</v>
+        <v>131.3412232983564</v>
       </c>
       <c r="D116" t="n">
-        <v>89.88226882463523</v>
-      </c>
-      <c r="E116" t="n">
-        <v>133.8408829176474</v>
-      </c>
-      <c r="F116" t="n">
-        <v>134.9300977315004</v>
+        <v>133.4511188068555</v>
       </c>
     </row>
     <row r="117">
@@ -2577,16 +1877,10 @@
         <v>8</v>
       </c>
       <c r="C117" t="n">
-        <v>50.29762036463427</v>
+        <v>129.5719405894621</v>
       </c>
       <c r="D117" t="n">
-        <v>89.88226882463523</v>
-      </c>
-      <c r="E117" t="n">
-        <v>130.9554027119842</v>
-      </c>
-      <c r="F117" t="n">
-        <v>235.2256819658314</v>
+        <v>233.0722369784407</v>
       </c>
     </row>
     <row r="118">
@@ -2595,16 +1889,10 @@
         <v>9</v>
       </c>
       <c r="C118" t="n">
-        <v>48.70496268315375</v>
+        <v>124.9599523102413</v>
       </c>
       <c r="D118" t="n">
-        <v>89.88226882463523</v>
-      </c>
-      <c r="E118" t="n">
-        <v>126.294171432583</v>
-      </c>
-      <c r="F118" t="n">
-        <v>192.3804798687446</v>
+        <v>190.6192743040166</v>
       </c>
     </row>
     <row r="119">
@@ -2613,16 +1901,10 @@
         <v>10</v>
       </c>
       <c r="C119" t="n">
-        <v>172.1251250297598</v>
+        <v>301.5959403827732</v>
       </c>
       <c r="D119" t="n">
-        <v>263.2266444150032</v>
-      </c>
-      <c r="E119" t="n">
-        <v>305.4295237688523</v>
-      </c>
-      <c r="F119" t="n">
-        <v>442.4020002801527</v>
+        <v>438.2300365579485</v>
       </c>
     </row>
     <row r="120">
@@ -2631,16 +1913,10 @@
         <v>11</v>
       </c>
       <c r="C120" t="n">
-        <v>102.3313359896386</v>
+        <v>148.3538550846816</v>
       </c>
       <c r="D120" t="n">
-        <v>121.9830791191478</v>
-      </c>
-      <c r="E120" t="n">
-        <v>150.3728750400337</v>
-      </c>
-      <c r="F120" t="n">
-        <v>183.4220398105006</v>
+        <v>181.6209868368472</v>
       </c>
     </row>
     <row r="121">
@@ -2649,16 +1925,10 @@
         <v>12</v>
       </c>
       <c r="C121" t="n">
-        <v>15.60903804324467</v>
+        <v>50.52526111876168</v>
       </c>
       <c r="D121" t="n">
-        <v>38.5209723534151</v>
-      </c>
-      <c r="E121" t="n">
-        <v>51.06472811038309</v>
-      </c>
-      <c r="F121" t="n">
-        <v>100.5038696621182</v>
+        <v>99.58377644555912</v>
       </c>
     </row>
     <row r="122">
@@ -2669,16 +1939,10 @@
         <v>1</v>
       </c>
       <c r="C122" t="n">
-        <v>56.06185160140818</v>
+        <v>90.50343033294267</v>
       </c>
       <c r="D122" t="n">
-        <v>70.62178264792769</v>
-      </c>
-      <c r="E122" t="n">
-        <v>91.46975118338555</v>
-      </c>
-      <c r="F122" t="n">
-        <v>103.7775273124616</v>
+        <v>102.8274644021231</v>
       </c>
     </row>
     <row r="123">
@@ -2687,16 +1951,10 @@
         <v>2</v>
       </c>
       <c r="C123" t="n">
-        <v>113.9361516688656</v>
+        <v>107.1667660330126</v>
       </c>
       <c r="D123" t="n">
-        <v>89.88226882463523</v>
-      </c>
-      <c r="E123" t="n">
-        <v>109.3139282945761</v>
-      </c>
-      <c r="F123" t="n">
-        <v>89.71181330284351</v>
+        <v>88.52493873342779</v>
       </c>
     </row>
     <row r="124">
@@ -2705,16 +1963,10 @@
         <v>3</v>
       </c>
       <c r="C124" t="n">
-        <v>103.4029007215408</v>
+        <v>128.3187127790467</v>
       </c>
       <c r="D124" t="n">
-        <v>96.30243088353775</v>
-      </c>
-      <c r="E124" t="n">
-        <v>130.1284125597465</v>
-      </c>
-      <c r="F124" t="n">
-        <v>142.4132423956961</v>
+        <v>140.9876169199833</v>
       </c>
     </row>
     <row r="125">
@@ -2723,16 +1975,10 @@
         <v>4</v>
       </c>
       <c r="C125" t="n">
-        <v>37.67007811739805</v>
+        <v>76.46805571215427</v>
       </c>
       <c r="D125" t="n">
-        <v>51.36129647122013</v>
-      </c>
-      <c r="E125" t="n">
-        <v>77.28451842915457</v>
-      </c>
-      <c r="F125" t="n">
-        <v>66.59948060090755</v>
+        <v>65.98977541708464</v>
       </c>
     </row>
     <row r="126">
@@ -2741,16 +1987,10 @@
         <v>5</v>
       </c>
       <c r="C126" t="n">
-        <v>183.3506201276976</v>
+        <v>243.3926125185314</v>
       </c>
       <c r="D126" t="n">
-        <v>179.7645376492705</v>
-      </c>
-      <c r="E126" t="n">
-        <v>245.9913577313392</v>
-      </c>
-      <c r="F126" t="n">
-        <v>214.2709272854572</v>
+        <v>212.3093189676485</v>
       </c>
     </row>
     <row r="127">
@@ -2759,16 +1999,10 @@
         <v>6</v>
       </c>
       <c r="C127" t="n">
-        <v>161.8121628948026</v>
+        <v>192.7634451700723</v>
       </c>
       <c r="D127" t="n">
-        <v>141.2435652958554</v>
-      </c>
-      <c r="E127" t="n">
-        <v>195.2925983213572</v>
-      </c>
-      <c r="F127" t="n">
-        <v>145.4162202692861</v>
+        <v>143.8412429492813</v>
       </c>
     </row>
     <row r="128">
@@ -2777,16 +2011,10 @@
         <v>7</v>
       </c>
       <c r="C128" t="n">
-        <v>56.83677085055741</v>
+        <v>65.57289702946214</v>
       </c>
       <c r="D128" t="n">
-        <v>64.20162058902517</v>
-      </c>
-      <c r="E128" t="n">
-        <v>66.91680607304407</v>
-      </c>
-      <c r="F128" t="n">
-        <v>109.3394145453973</v>
+        <v>108.0947133066346</v>
       </c>
     </row>
     <row r="129">
@@ -2795,16 +2023,10 @@
         <v>8</v>
       </c>
       <c r="C129" t="n">
-        <v>97.47372606023418</v>
+        <v>79.6755823150408</v>
       </c>
       <c r="D129" t="n">
-        <v>48.15121544176888</v>
-      </c>
-      <c r="E129" t="n">
-        <v>81.90886943012093</v>
-      </c>
-      <c r="F129" t="n">
-        <v>110.3397149419136</v>
+        <v>109.1772512772822</v>
       </c>
     </row>
     <row r="130">
@@ -2813,16 +2035,10 @@
         <v>9</v>
       </c>
       <c r="C130" t="n">
-        <v>3.561390665038996</v>
+        <v>18.20480696215047</v>
       </c>
       <c r="D130" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E130" t="n">
-        <v>18.39918284913174</v>
-      </c>
-      <c r="F130" t="n">
-        <v>52.40874969493209</v>
+        <v>51.92895786955498</v>
       </c>
     </row>
     <row r="131">
@@ -2831,16 +2047,10 @@
         <v>10</v>
       </c>
       <c r="C131" t="n">
-        <v>100.9378823057689</v>
+        <v>88.68990099911647</v>
       </c>
       <c r="D131" t="n">
-        <v>88.2772283099096</v>
-      </c>
-      <c r="E131" t="n">
-        <v>90.33277412004396</v>
-      </c>
-      <c r="F131" t="n">
-        <v>95.36590874916129</v>
+        <v>94.18820213017318</v>
       </c>
     </row>
     <row r="132">
@@ -2849,16 +2059,10 @@
         <v>11</v>
       </c>
       <c r="C132" t="n">
-        <v>70.64865325592929</v>
+        <v>120.303177937616</v>
       </c>
       <c r="D132" t="n">
-        <v>96.30243088353775</v>
-      </c>
-      <c r="E132" t="n">
-        <v>121.9093645972343</v>
-      </c>
-      <c r="F132" t="n">
-        <v>141.180315998116</v>
+        <v>139.735512679083</v>
       </c>
     </row>
     <row r="133">
@@ -2867,16 +2071,10 @@
         <v>12</v>
       </c>
       <c r="C133" t="n">
-        <v>53.23966604677005</v>
+        <v>44.71615914602059</v>
       </c>
       <c r="D133" t="n">
-        <v>40.12601286814073</v>
-      </c>
-      <c r="E133" t="n">
-        <v>45.68681669930588</v>
-      </c>
-      <c r="F133" t="n">
-        <v>61.63109533443043</v>
+        <v>60.91454952987213</v>
       </c>
     </row>
     <row r="134">
@@ -2887,16 +2085,10 @@
         <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>64.71294478317611</v>
+        <v>64.17471568928146</v>
       </c>
       <c r="D134" t="n">
-        <v>64.20162058902517</v>
-      </c>
-      <c r="E134" t="n">
-        <v>65.6244040756721</v>
-      </c>
-      <c r="F134" t="n">
-        <v>84.2655184868146</v>
+        <v>83.18943376373835</v>
       </c>
     </row>
     <row r="135">
@@ -2905,16 +2097,10 @@
         <v>2</v>
       </c>
       <c r="C135" t="n">
-        <v>80.26173177496307</v>
+        <v>94.0456591725786</v>
       </c>
       <c r="D135" t="n">
-        <v>88.2772283099096</v>
-      </c>
-      <c r="E135" t="n">
-        <v>95.68145226949586</v>
-      </c>
-      <c r="F135" t="n">
-        <v>140.3743982691956</v>
+        <v>138.7846477554383</v>
       </c>
     </row>
     <row r="136">
@@ -2923,16 +2109,10 @@
         <v>3</v>
       </c>
       <c r="C136" t="n">
-        <v>74.20220957300671</v>
+        <v>98.48818682151283</v>
       </c>
       <c r="D136" t="n">
-        <v>88.2772283099096</v>
-      </c>
-      <c r="E136" t="n">
-        <v>99.86961571916261</v>
-      </c>
-      <c r="F136" t="n">
-        <v>124.0681083977813</v>
+        <v>122.779963983389</v>
       </c>
     </row>
     <row r="137">
@@ -2941,16 +2121,10 @@
         <v>4</v>
       </c>
       <c r="C137" t="n">
-        <v>107.9802094927135</v>
+        <v>113.6254957044655</v>
       </c>
       <c r="D137" t="n">
-        <v>128.4032411780503</v>
-      </c>
-      <c r="E137" t="n">
-        <v>116.0691066555185</v>
-      </c>
-      <c r="F137" t="n">
-        <v>168.5310369736292</v>
+        <v>166.3788675274767</v>
       </c>
     </row>
     <row r="138">
@@ -2959,16 +2133,10 @@
         <v>5</v>
       </c>
       <c r="C138" t="n">
-        <v>114.6379720185124</v>
+        <v>95.29106131696646</v>
       </c>
       <c r="D138" t="n">
-        <v>102.7225929424403</v>
-      </c>
-      <c r="E138" t="n">
-        <v>97.75654783831435</v>
-      </c>
-      <c r="F138" t="n">
-        <v>97.31560226459723</v>
+        <v>95.81539615687515</v>
       </c>
     </row>
     <row r="139">
@@ -2977,16 +2145,10 @@
         <v>6</v>
       </c>
       <c r="C139" t="n">
-        <v>105.4423602400155</v>
+        <v>159.6727373789095</v>
       </c>
       <c r="D139" t="n">
-        <v>128.4032411780503</v>
-      </c>
-      <c r="E139" t="n">
-        <v>161.9625124372043</v>
-      </c>
-      <c r="F139" t="n">
-        <v>210.1568377878998</v>
+        <v>207.9891728110418</v>
       </c>
     </row>
     <row r="140">
@@ -2995,16 +2157,10 @@
         <v>7</v>
       </c>
       <c r="C140" t="n">
-        <v>99.29242264704618</v>
+        <v>136.2113318648065</v>
       </c>
       <c r="D140" t="n">
-        <v>134.8234032369529</v>
-      </c>
-      <c r="E140" t="n">
-        <v>138.420912466535</v>
-      </c>
-      <c r="F140" t="n">
-        <v>233.8710308693412</v>
+        <v>231.3644069347187</v>
       </c>
     </row>
     <row r="141">
@@ -3013,16 +2169,10 @@
         <v>8</v>
       </c>
       <c r="C141" t="n">
-        <v>55.3279272349284</v>
+        <v>28.9706768276505</v>
       </c>
       <c r="D141" t="n">
-        <v>12.84032411780503</v>
-      </c>
-      <c r="E141" t="n">
-        <v>30.11846787740072</v>
-      </c>
-      <c r="F141" t="n">
-        <v>4.417772441639554</v>
+        <v>4.255468430537768</v>
       </c>
     </row>
     <row r="142">
@@ -3031,16 +2181,10 @@
         <v>9</v>
       </c>
       <c r="C142" t="n">
-        <v>88.94062206628506</v>
+        <v>169.9348060889445</v>
       </c>
       <c r="D142" t="n">
-        <v>134.8234032369529</v>
-      </c>
-      <c r="E142" t="n">
-        <v>171.7492295393664</v>
-      </c>
-      <c r="F142" t="n">
-        <v>313.41252609219</v>
+        <v>310.543295880343</v>
       </c>
     </row>
     <row r="143">
@@ -3049,16 +2193,10 @@
         <v>10</v>
       </c>
       <c r="C143" t="n">
-        <v>103.9024360717319</v>
+        <v>75.93019709849074</v>
       </c>
       <c r="D143" t="n">
-        <v>109.1427550013428</v>
-      </c>
-      <c r="E143" t="n">
-        <v>78.02185905521674</v>
-      </c>
-      <c r="F143" t="n">
-        <v>113.3207382316878</v>
+        <v>111.5521480722305</v>
       </c>
     </row>
     <row r="144">
@@ -3067,16 +2205,10 @@
         <v>11</v>
       </c>
       <c r="C144" t="n">
-        <v>94.26111989536139</v>
+        <v>114.2499453433851</v>
       </c>
       <c r="D144" t="n">
-        <v>89.88226882463523</v>
-      </c>
-      <c r="E144" t="n">
-        <v>116.0235790847823</v>
-      </c>
-      <c r="F144" t="n">
-        <v>109.6529681257816</v>
+        <v>108.4053963654827</v>
       </c>
     </row>
     <row r="145">
@@ -3085,16 +2217,10 @@
         <v>12</v>
       </c>
       <c r="C145" t="n">
-        <v>215.8650318966562</v>
+        <v>289.604344366576</v>
       </c>
       <c r="D145" t="n">
-        <v>192.6048617670755</v>
-      </c>
-      <c r="E145" t="n">
-        <v>293.4567912849363</v>
-      </c>
-      <c r="F145" t="n">
-        <v>371.387535618857</v>
+        <v>367.7438352229243</v>
       </c>
     </row>
     <row r="146">
@@ -3105,16 +2231,10 @@
         <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>112.6573917526453</v>
+        <v>84.19176056370704</v>
       </c>
       <c r="D146" t="n">
-        <v>109.1427550013428</v>
-      </c>
-      <c r="E146" t="n">
-        <v>86.3957508247257</v>
-      </c>
-      <c r="F146" t="n">
-        <v>88.04360862596901</v>
+        <v>86.50642563085771</v>
       </c>
     </row>
     <row r="147">
@@ -3123,16 +2243,10 @@
         <v>2</v>
       </c>
       <c r="C147" t="n">
-        <v>167.0130547886146</v>
+        <v>128.3539201188285</v>
       </c>
       <c r="D147" t="n">
-        <v>115.5629170602453</v>
-      </c>
-      <c r="E147" t="n">
-        <v>131.0418403257972</v>
-      </c>
-      <c r="F147" t="n">
-        <v>83.29465558157737</v>
+        <v>81.80094832025217</v>
       </c>
     </row>
     <row r="148">
@@ -3141,16 +2255,10 @@
         <v>3</v>
       </c>
       <c r="C148" t="n">
-        <v>125.5180440126273</v>
+        <v>124.2981685832153</v>
       </c>
       <c r="D148" t="n">
-        <v>115.5629170602453</v>
-      </c>
-      <c r="E148" t="n">
-        <v>126.7140106928284</v>
-      </c>
-      <c r="F148" t="n">
-        <v>143.7656426147795</v>
+        <v>141.962055667931</v>
       </c>
     </row>
     <row r="149">
@@ -3159,16 +2267,10 @@
         <v>4</v>
       </c>
       <c r="C149" t="n">
-        <v>98.20066678561319</v>
+        <v>74.96760609449733</v>
       </c>
       <c r="D149" t="n">
-        <v>96.30243088353775</v>
-      </c>
-      <c r="E149" t="n">
-        <v>76.89204604870395</v>
-      </c>
-      <c r="F149" t="n">
-        <v>83.62583618432946</v>
+        <v>82.25095720031995</v>
       </c>
     </row>
     <row r="150">
@@ -3177,16 +2279,10 @@
         <v>5</v>
       </c>
       <c r="C150" t="n">
-        <v>86.75743964458768</v>
+        <v>64.12186274328741</v>
       </c>
       <c r="D150" t="n">
-        <v>57.78145853012265</v>
-      </c>
-      <c r="E150" t="n">
-        <v>65.37698200520116</v>
-      </c>
-      <c r="F150" t="n">
-        <v>34.36572724338335</v>
+        <v>33.80739540849456</v>
       </c>
     </row>
     <row r="151">
@@ -3195,16 +2291,10 @@
         <v>6</v>
       </c>
       <c r="C151" t="n">
-        <v>138.2573794990228</v>
+        <v>113.8652524049284</v>
       </c>
       <c r="D151" t="n">
-        <v>112.3528360307941</v>
-      </c>
-      <c r="E151" t="n">
-        <v>116.7157567144686</v>
-      </c>
-      <c r="F151" t="n">
-        <v>122.183732110118</v>
+        <v>120.455863150644</v>
       </c>
     </row>
     <row r="152">
@@ -3213,16 +2303,10 @@
         <v>7</v>
       </c>
       <c r="C152" t="n">
-        <v>82.29365049703101</v>
+        <v>84.57252889824471</v>
       </c>
       <c r="D152" t="n">
-        <v>96.30243088353775</v>
-      </c>
-      <c r="E152" t="n">
-        <v>86.51161865691316</v>
-      </c>
-      <c r="F152" t="n">
-        <v>101.0829411219215</v>
+        <v>99.51695355629839</v>
       </c>
     </row>
     <row r="153">
@@ -3231,16 +2315,10 @@
         <v>8</v>
       </c>
       <c r="C153" t="n">
-        <v>19.76268053462466</v>
+        <v>46.55924595244649</v>
       </c>
       <c r="D153" t="n">
-        <v>32.10081029451258</v>
-      </c>
-      <c r="E153" t="n">
-        <v>47.1370452925706</v>
-      </c>
-      <c r="F153" t="n">
-        <v>61.98183133354255</v>
+        <v>61.33028807833652</v>
       </c>
     </row>
     <row r="154">
@@ -3249,16 +2327,10 @@
         <v>9</v>
       </c>
       <c r="C154" t="n">
-        <v>36.42639127219083</v>
+        <v>54.90089440545302</v>
       </c>
       <c r="D154" t="n">
-        <v>50.44413046280548</v>
-      </c>
-      <c r="E154" t="n">
-        <v>55.79802211865944</v>
-      </c>
-      <c r="F154" t="n">
-        <v>77.03014747059002</v>
+        <v>76.15379685320005</v>
       </c>
     </row>
     <row r="155">
@@ -3267,16 +2339,10 @@
         <v>10</v>
       </c>
       <c r="C155" t="n">
-        <v>114.6824298763383</v>
+        <v>99.76518481251124</v>
       </c>
       <c r="D155" t="n">
-        <v>87.1307707993913</v>
-      </c>
-      <c r="E155" t="n">
-        <v>101.7719372149969</v>
-      </c>
-      <c r="F155" t="n">
-        <v>99.29763540741988</v>
+        <v>98.04041311237535</v>
       </c>
     </row>
     <row r="156">
@@ -3285,16 +2351,10 @@
         <v>11</v>
       </c>
       <c r="C156" t="n">
-        <v>36.74312104138227</v>
+        <v>58.3807740643126</v>
       </c>
       <c r="D156" t="n">
-        <v>72.22682316265332</v>
-      </c>
-      <c r="E156" t="n">
-        <v>59.25324443056444</v>
-      </c>
-      <c r="F156" t="n">
-        <v>125.9962389321686</v>
+        <v>124.7102083392262</v>
       </c>
     </row>
     <row r="157">
@@ -3303,16 +2363,10 @@
         <v>12</v>
       </c>
       <c r="C157" t="n">
-        <v>88.85149010499784</v>
+        <v>79.37715012603735</v>
       </c>
       <c r="D157" t="n">
-        <v>112.3528360307941</v>
-      </c>
-      <c r="E157" t="n">
-        <v>80.9896383658479</v>
-      </c>
-      <c r="F157" t="n">
-        <v>66.30738013657532</v>
+        <v>65.09684683468716</v>
       </c>
     </row>
     <row r="158">
@@ -3323,16 +2377,10 @@
         <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>72.47815464411468</v>
+        <v>68.02082165121021</v>
       </c>
       <c r="D158" t="n">
-        <v>67.76837728841546</v>
-      </c>
-      <c r="E158" t="n">
-        <v>69.12997687522726</v>
-      </c>
-      <c r="F158" t="n">
-        <v>39.52780089952044</v>
+        <v>38.85124101917794</v>
       </c>
     </row>
     <row r="159">
@@ -3341,16 +2389,10 @@
         <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>78.70366669474559</v>
+        <v>91.88890590554387</v>
       </c>
       <c r="D159" t="n">
-        <v>114.1362143804892</v>
-      </c>
-      <c r="E159" t="n">
-        <v>93.50419774439166</v>
-      </c>
-      <c r="F159" t="n">
-        <v>119.9211248381788</v>
+        <v>118.1542613780017</v>
       </c>
     </row>
     <row r="160">
@@ -3359,16 +2401,10 @@
         <v>3</v>
       </c>
       <c r="C160" t="n">
-        <v>89.2832033295801</v>
+        <v>96.41890488170711</v>
       </c>
       <c r="D160" t="n">
-        <v>85.60216078536689</v>
-      </c>
-      <c r="E160" t="n">
-        <v>97.56839250279648</v>
-      </c>
-      <c r="F160" t="n">
-        <v>74.72303834627914</v>
+        <v>73.81548561099636</v>
       </c>
     </row>
     <row r="161">
@@ -3377,16 +2413,10 @@
         <v>4</v>
       </c>
       <c r="C161" t="n">
-        <v>59.83942636911318</v>
+        <v>59.9014166962174</v>
       </c>
       <c r="D161" t="n">
-        <v>67.76837728841546</v>
-      </c>
-      <c r="E161" t="n">
-        <v>60.8797078299685</v>
-      </c>
-      <c r="F161" t="n">
-        <v>57.85346018844796</v>
+        <v>57.00913249123035</v>
       </c>
     </row>
     <row r="162">
@@ -3395,16 +2425,10 @@
         <v>5</v>
       </c>
       <c r="C162" t="n">
-        <v>45.7409413890817</v>
+        <v>52.26218812083945</v>
       </c>
       <c r="D162" t="n">
-        <v>39.23432369329316</v>
-      </c>
-      <c r="E162" t="n">
-        <v>52.90502887219936</v>
-      </c>
-      <c r="F162" t="n">
-        <v>32.38341756573869</v>
+        <v>31.94250461904481</v>
       </c>
     </row>
     <row r="163">
@@ -3413,16 +2437,10 @@
         <v>6</v>
       </c>
       <c r="C163" t="n">
-        <v>49.80812028947318</v>
+        <v>51.72065975604874</v>
       </c>
       <c r="D163" t="n">
-        <v>56.17641801539703</v>
-      </c>
-      <c r="E163" t="n">
-        <v>52.56042460241247</v>
-      </c>
-      <c r="F163" t="n">
-        <v>38.15344732576637</v>
+        <v>37.55880600603283</v>
       </c>
     </row>
     <row r="164">
@@ -3431,16 +2449,10 @@
         <v>7</v>
       </c>
       <c r="C164" t="n">
-        <v>22.25277891042477</v>
+        <v>19.24039332368387</v>
       </c>
       <c r="D164" t="n">
-        <v>25.68064823561006</v>
-      </c>
-      <c r="E164" t="n">
-        <v>19.60000442239541</v>
-      </c>
-      <c r="F164" t="n">
-        <v>16.63923708882841</v>
+        <v>16.35485207371715</v>
       </c>
     </row>
     <row r="165">
@@ -3449,16 +2461,10 @@
         <v>8</v>
       </c>
       <c r="C165" t="n">
-        <v>31.46583763282788</v>
+        <v>22.48724943774749</v>
       </c>
       <c r="D165" t="n">
-        <v>19.26048617670755</v>
-      </c>
-      <c r="E165" t="n">
-        <v>23.13255869496553</v>
-      </c>
-      <c r="F165" t="n">
-        <v>12.93168628647601</v>
+        <v>12.70725144650826</v>
       </c>
     </row>
     <row r="166">
@@ -3467,16 +2473,10 @@
         <v>9</v>
       </c>
       <c r="C166" t="n">
-        <v>28.53580300584759</v>
+        <v>37.37733109466252</v>
       </c>
       <c r="D166" t="n">
-        <v>44.94113441231762</v>
-      </c>
-      <c r="E166" t="n">
-        <v>38.11811816607767</v>
-      </c>
-      <c r="F166" t="n">
-        <v>55.97683127094221</v>
+        <v>55.17964004221952</v>
       </c>
     </row>
     <row r="167">
@@ -3485,16 +2485,10 @@
         <v>10</v>
       </c>
       <c r="C167" t="n">
-        <v>64.41893411454211</v>
+        <v>82.06668238512991</v>
       </c>
       <c r="D167" t="n">
-        <v>75.87464251430248</v>
-      </c>
-      <c r="E167" t="n">
-        <v>83.26540939435196</v>
-      </c>
-      <c r="F167" t="n">
-        <v>97.55412388384026</v>
+        <v>96.43206740273311</v>
       </c>
     </row>
     <row r="168">
@@ -3503,16 +2497,10 @@
         <v>11</v>
       </c>
       <c r="C168" t="n">
-        <v>58.61554650671795</v>
+        <v>43.03557219295082</v>
       </c>
       <c r="D168" t="n">
-        <v>67.11987607034449</v>
-      </c>
-      <c r="E168" t="n">
-        <v>44.26401217234739</v>
-      </c>
-      <c r="F168" t="n">
-        <v>43.76796352564332</v>
+        <v>42.9103747070696</v>
       </c>
     </row>
     <row r="169">
@@ -3521,16 +2509,10 @@
         <v>12</v>
       </c>
       <c r="C169" t="n">
-        <v>37.70562354173397</v>
+        <v>47.61608632164597</v>
       </c>
       <c r="D169" t="n">
-        <v>43.77383221978989</v>
-      </c>
-      <c r="E169" t="n">
-        <v>48.25034598761391</v>
-      </c>
-      <c r="F169" t="n">
-        <v>48.41262491824883</v>
+        <v>47.78657121687186</v>
       </c>
     </row>
     <row r="170">
@@ -3541,16 +2523,10 @@
         <v>1</v>
       </c>
       <c r="C170" t="n">
-        <v>11.50688874155122</v>
+        <v>13.59549794003821</v>
       </c>
       <c r="D170" t="n">
-        <v>26.26429933187393</v>
-      </c>
-      <c r="E170" t="n">
-        <v>13.8622532886866</v>
-      </c>
-      <c r="F170" t="n">
-        <v>19.35676541092898</v>
+        <v>19.00298408380852</v>
       </c>
     </row>
     <row r="171">
@@ -3559,16 +2535,10 @@
         <v>2</v>
       </c>
       <c r="C171" t="n">
-        <v>68.43816064579576</v>
+        <v>82.01829645610631</v>
       </c>
       <c r="D171" t="n">
-        <v>102.1389418461764</v>
-      </c>
-      <c r="E171" t="n">
-        <v>83.52428137277899</v>
-      </c>
-      <c r="F171" t="n">
-        <v>103.7971292998955</v>
+        <v>102.2930318145118</v>
       </c>
     </row>
     <row r="172">
@@ -3577,16 +2547,10 @@
         <v>3</v>
       </c>
       <c r="C172" t="n">
-        <v>57.06907580655505</v>
+        <v>54.54336194831857</v>
       </c>
       <c r="D172" t="n">
-        <v>55.44685414506719</v>
-      </c>
-      <c r="E172" t="n">
-        <v>55.35053124056097</v>
-      </c>
-      <c r="F172" t="n">
-        <v>33.70335035554638</v>
+        <v>33.16907575381832</v>
       </c>
     </row>
     <row r="173">
@@ -3595,16 +2559,10 @@
         <v>4</v>
       </c>
       <c r="C173" t="n">
-        <v>55.24704439094108</v>
+        <v>64.2807768733998</v>
       </c>
       <c r="D173" t="n">
-        <v>52.52859866374786</v>
-      </c>
-      <c r="E173" t="n">
-        <v>65.28063622827906</v>
-      </c>
-      <c r="F173" t="n">
-        <v>47.69823479425632</v>
+        <v>47.01709232392517</v>
       </c>
     </row>
     <row r="174">
@@ -3613,16 +2571,10 @@
         <v>5</v>
       </c>
       <c r="C174" t="n">
-        <v>76.16620663147549</v>
+        <v>88.62318852062427</v>
       </c>
       <c r="D174" t="n">
-        <v>75.87464251430248</v>
-      </c>
-      <c r="E174" t="n">
-        <v>89.88991905423948</v>
-      </c>
-      <c r="F174" t="n">
-        <v>96.75898331132132</v>
+        <v>95.6977318420255</v>
       </c>
     </row>
     <row r="175">
@@ -3631,16 +2583,10 @@
         <v>6</v>
       </c>
       <c r="C175" t="n">
-        <v>61.09937466577962</v>
+        <v>70.99520646723164</v>
       </c>
       <c r="D175" t="n">
-        <v>72.95638703298314</v>
-      </c>
-      <c r="E175" t="n">
-        <v>72.453519724212</v>
-      </c>
-      <c r="F175" t="n">
-        <v>78.45558097282368</v>
+        <v>77.15690678254117</v>
       </c>
     </row>
     <row r="176">
@@ -3649,16 +2595,10 @@
         <v>7</v>
       </c>
       <c r="C176" t="n">
-        <v>71.52648054316478</v>
+        <v>61.98197665382559</v>
       </c>
       <c r="D176" t="n">
-        <v>40.85557673847057</v>
-      </c>
-      <c r="E176" t="n">
-        <v>62.99207270635667</v>
-      </c>
-      <c r="F176" t="n">
-        <v>21.07905550541424</v>
+        <v>20.73428281934729</v>
       </c>
     </row>
     <row r="177">
@@ -3667,16 +2607,10 @@
         <v>8</v>
       </c>
       <c r="C177" t="n">
-        <v>66.16902144359327</v>
+        <v>72.3660621634654</v>
       </c>
       <c r="D177" t="n">
-        <v>29.18255481319326</v>
-      </c>
-      <c r="E177" t="n">
-        <v>73.18726364071649</v>
-      </c>
-      <c r="F177" t="n">
-        <v>21.24651263989524</v>
+        <v>20.98734500399812</v>
       </c>
     </row>
     <row r="178">
@@ -3685,16 +2619,10 @@
         <v>9</v>
       </c>
       <c r="C178" t="n">
-        <v>47.75473347826359</v>
+        <v>37.91461372449604</v>
       </c>
       <c r="D178" t="n">
-        <v>40.85557673847057</v>
-      </c>
-      <c r="E178" t="n">
-        <v>38.81687782779194</v>
-      </c>
-      <c r="F178" t="n">
-        <v>34.52454734685674</v>
+        <v>33.96327405371022</v>
       </c>
     </row>
     <row r="179">
@@ -3703,16 +2631,10 @@
         <v>10</v>
       </c>
       <c r="C179" t="n">
-        <v>62.82168250046322</v>
+        <v>64.20861456525505</v>
       </c>
       <c r="D179" t="n">
-        <v>67.11987607034449</v>
-      </c>
-      <c r="E179" t="n">
-        <v>65.20862948196124</v>
-      </c>
-      <c r="F179" t="n">
-        <v>46.60342816555469</v>
+        <v>45.90042907778962</v>
       </c>
     </row>
     <row r="180">
@@ -3721,16 +2643,10 @@
         <v>11</v>
       </c>
       <c r="C180" t="n">
-        <v>51.31408427972681</v>
+        <v>65.33698821760566</v>
       </c>
       <c r="D180" t="n">
-        <v>52.52859866374786</v>
-      </c>
-      <c r="E180" t="n">
-        <v>66.32969807435792</v>
-      </c>
-      <c r="F180" t="n">
-        <v>52.8069295892776</v>
+        <v>52.13878155950879</v>
       </c>
     </row>
     <row r="181">
@@ -3739,16 +2655,10 @@
         <v>12</v>
       </c>
       <c r="C181" t="n">
-        <v>44.48417040072802</v>
+        <v>37.57518962246321</v>
       </c>
       <c r="D181" t="n">
-        <v>26.26429933187393</v>
-      </c>
-      <c r="E181" t="n">
-        <v>38.41563718825957</v>
-      </c>
-      <c r="F181" t="n">
-        <v>29.16288873174845</v>
+        <v>28.76148234516863</v>
       </c>
     </row>
     <row r="182">
@@ -3759,16 +2669,10 @@
         <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>43.12393924141057</v>
+        <v>44.0725561998437</v>
       </c>
       <c r="D182" t="n">
-        <v>26.75067524542715</v>
-      </c>
-      <c r="E182" t="n">
-        <v>44.73621230310104</v>
-      </c>
-      <c r="F182" t="n">
-        <v>19.68459703940573</v>
+        <v>19.38287459607224</v>
       </c>
     </row>
     <row r="183">
@@ -3777,16 +2681,10 @@
         <v>2</v>
       </c>
       <c r="C183" t="n">
-        <v>20.12215187480999</v>
+        <v>21.17703773691793</v>
       </c>
       <c r="D183" t="n">
-        <v>29.18255481319326</v>
-      </c>
-      <c r="E183" t="n">
-        <v>21.47804615464803</v>
-      </c>
-      <c r="F183" t="n">
-        <v>22.96852240572141</v>
+        <v>22.58817899120978</v>
       </c>
     </row>
     <row r="184">
@@ -3795,16 +2693,10 @@
         <v>3</v>
       </c>
       <c r="C184" t="n">
-        <v>32.38788858931938</v>
+        <v>25.96371219925803</v>
       </c>
       <c r="D184" t="n">
-        <v>37.93732125715124</v>
-      </c>
-      <c r="E184" t="n">
-        <v>26.58589838139238</v>
-      </c>
-      <c r="F184" t="n">
-        <v>28.68081050426494</v>
+        <v>28.12488067658932</v>
       </c>
     </row>
     <row r="185">
@@ -3813,16 +2705,10 @@
         <v>4</v>
       </c>
       <c r="C185" t="n">
-        <v>29.34842041591278</v>
+        <v>25.49581352254539</v>
       </c>
       <c r="D185" t="n">
-        <v>29.18255481319326</v>
-      </c>
-      <c r="E185" t="n">
-        <v>25.85496897516048</v>
-      </c>
-      <c r="F185" t="n">
-        <v>20.08464636695313</v>
+        <v>19.7737226063297</v>
       </c>
     </row>
     <row r="186">
@@ -3831,16 +2717,10 @@
         <v>5</v>
       </c>
       <c r="C186" t="n">
-        <v>17.29091585691813</v>
+        <v>29.30387070685258</v>
       </c>
       <c r="D186" t="n">
-        <v>43.77383221978989</v>
-      </c>
-      <c r="E186" t="n">
-        <v>29.72547157458176</v>
-      </c>
-      <c r="F186" t="n">
-        <v>56.24514260382922</v>
+        <v>55.46161202632676</v>
       </c>
     </row>
     <row r="187">
@@ -3849,16 +2729,10 @@
         <v>6</v>
       </c>
       <c r="C187" t="n">
-        <v>28.08586702079545</v>
+        <v>49.95146026415152</v>
       </c>
       <c r="D187" t="n">
-        <v>67.11987607034449</v>
-      </c>
-      <c r="E187" t="n">
-        <v>50.76124654514981</v>
-      </c>
-      <c r="F187" t="n">
-        <v>83.46780346598635</v>
+        <v>82.19894845245128</v>
       </c>
     </row>
     <row r="188">
@@ -3867,16 +2741,10 @@
         <v>7</v>
       </c>
       <c r="C188" t="n">
-        <v>61.57627715538388</v>
+        <v>41.27914845701473</v>
       </c>
       <c r="D188" t="n">
-        <v>69.55175563811059</v>
-      </c>
-      <c r="E188" t="n">
-        <v>42.55466939008122</v>
-      </c>
-      <c r="F188" t="n">
-        <v>41.68455072200318</v>
+        <v>40.72946814549363</v>
       </c>
     </row>
     <row r="189">
@@ -3885,16 +2753,10 @@
         <v>8</v>
       </c>
       <c r="C189" t="n">
-        <v>3.427741639326958</v>
+        <v>4.606556298244054</v>
       </c>
       <c r="D189" t="n">
-        <v>16.05040514725629</v>
-      </c>
-      <c r="E189" t="n">
-        <v>4.697448165111483</v>
-      </c>
-      <c r="F189" t="n">
-        <v>13.93311079996179</v>
+        <v>13.68334183239159</v>
       </c>
     </row>
     <row r="190">
@@ -3903,16 +2765,10 @@
         <v>9</v>
       </c>
       <c r="C190" t="n">
-        <v>53.49351648554728</v>
+        <v>88.4003559912319</v>
       </c>
       <c r="D190" t="n">
-        <v>55.02996050487872</v>
-      </c>
-      <c r="E190" t="n">
-        <v>89.61969482006276</v>
-      </c>
-      <c r="F190" t="n">
-        <v>48.09837857415356</v>
+        <v>47.33408778138333</v>
       </c>
     </row>
     <row r="191">
@@ -3921,16 +2777,10 @@
         <v>10</v>
       </c>
       <c r="C191" t="n">
-        <v>92.39303652487951</v>
+        <v>103.4036961070118</v>
       </c>
       <c r="D191" t="n">
-        <v>66.49453561006177</v>
-      </c>
-      <c r="E191" t="n">
-        <v>105.1516099461831</v>
-      </c>
-      <c r="F191" t="n">
-        <v>55.8377938779393</v>
+        <v>54.73492902819333</v>
       </c>
     </row>
     <row r="192">
@@ -3939,16 +2789,10 @@
         <v>11</v>
       </c>
       <c r="C192" t="n">
-        <v>39.7954507926414</v>
+        <v>60.07941466185029</v>
       </c>
       <c r="D192" t="n">
-        <v>52.7370454838421</v>
-      </c>
-      <c r="E192" t="n">
-        <v>61.0689073528833</v>
-      </c>
-      <c r="F192" t="n">
-        <v>54.00458027980599</v>
+        <v>53.17345919250041</v>
       </c>
     </row>
     <row r="193">
@@ -3957,16 +2801,10 @@
         <v>12</v>
       </c>
       <c r="C193" t="n">
-        <v>16.42650967768552</v>
+        <v>11.83096747089867</v>
       </c>
       <c r="D193" t="n">
-        <v>36.38091833378093</v>
-      </c>
-      <c r="E193" t="n">
-        <v>12.14382363158929</v>
-      </c>
-      <c r="F193" t="n">
-        <v>21.74261790526631</v>
+        <v>21.28119697474801</v>
       </c>
     </row>
     <row r="194">
@@ -3977,16 +2815,10 @@
         <v>1</v>
       </c>
       <c r="C194" t="n">
-        <v>42.00877439400823</v>
+        <v>39.2271993225707</v>
       </c>
       <c r="D194" t="n">
-        <v>77.04194470683019</v>
-      </c>
-      <c r="E194" t="n">
-        <v>39.92914421695365</v>
-      </c>
-      <c r="F194" t="n">
-        <v>56.44470022396849</v>
+        <v>55.43108857637547</v>
       </c>
     </row>
     <row r="195">
@@ -3995,16 +2827,10 @@
         <v>2</v>
       </c>
       <c r="C195" t="n">
-        <v>66.05350268215609</v>
+        <v>83.37739154621589</v>
       </c>
       <c r="D195" t="n">
-        <v>81.32205274609854</v>
-      </c>
-      <c r="E195" t="n">
-        <v>84.49326575323933</v>
-      </c>
-      <c r="F195" t="n">
-        <v>86.25537352366784</v>
+        <v>85.04397074815431</v>
       </c>
     </row>
     <row r="196">
@@ -4013,16 +2839,10 @@
         <v>3</v>
       </c>
       <c r="C196" t="n">
-        <v>52.60900352976908</v>
+        <v>54.6266682908339</v>
       </c>
       <c r="D196" t="n">
-        <v>92.02232284426941</v>
-      </c>
-      <c r="E196" t="n">
-        <v>55.56195771551027</v>
-      </c>
-      <c r="F196" t="n">
-        <v>64.92221309717331</v>
+        <v>63.67401246345003</v>
       </c>
     </row>
     <row r="197">
@@ -4031,16 +2851,10 @@
         <v>4</v>
       </c>
       <c r="C197" t="n">
-        <v>50.51462271808671</v>
+        <v>39.31146250586026</v>
       </c>
       <c r="D197" t="n">
-        <v>53.50135049085431</v>
-      </c>
-      <c r="E197" t="n">
-        <v>40.19525248789162</v>
-      </c>
-      <c r="F197" t="n">
-        <v>33.13801003831774</v>
+        <v>32.48955810372646</v>
       </c>
     </row>
     <row r="198">
@@ -4049,16 +2863,10 @@
         <v>5</v>
       </c>
       <c r="C198" t="n">
-        <v>23.59254525934591</v>
+        <v>19.07011441041341</v>
       </c>
       <c r="D198" t="n">
-        <v>47.08118843195179</v>
-      </c>
-      <c r="E198" t="n">
-        <v>19.41017942422767</v>
-      </c>
-      <c r="F198" t="n">
-        <v>34.2686019013057</v>
+        <v>33.64068579548895</v>
       </c>
     </row>
     <row r="199">
@@ -4067,16 +2875,10 @@
         <v>6</v>
       </c>
       <c r="C199" t="n">
-        <v>108.985598090651</v>
+        <v>144.2380556426494</v>
       </c>
       <c r="D199" t="n">
-        <v>42.13231351154776</v>
-      </c>
-      <c r="E199" t="n">
-        <v>145.7103388635697</v>
-      </c>
-      <c r="F199" t="n">
-        <v>42.94318568266863</v>
+        <v>42.40837351079914</v>
       </c>
     </row>
     <row r="200">
@@ -4085,16 +2887,10 @@
         <v>7</v>
       </c>
       <c r="C200" t="n">
-        <v>39.26466266824162</v>
+        <v>29.18831553527226</v>
       </c>
       <c r="D200" t="n">
-        <v>44.1386141549548</v>
-      </c>
-      <c r="E200" t="n">
-        <v>30.11426587903243</v>
-      </c>
-      <c r="F200" t="n">
-        <v>35.44596823798166</v>
+        <v>34.73554039106627</v>
       </c>
     </row>
     <row r="201">
@@ -4103,16 +2899,10 @@
         <v>8</v>
       </c>
       <c r="C201" t="n">
-        <v>12.1714056921689</v>
+        <v>12.90972192057039</v>
       </c>
       <c r="D201" t="n">
-        <v>22.0693070774774</v>
-      </c>
-      <c r="E201" t="n">
-        <v>13.17398444927232</v>
-      </c>
-      <c r="F201" t="n">
-        <v>22.82310083098642</v>
+        <v>22.48373384973021</v>
       </c>
     </row>
     <row r="202">
@@ -4121,16 +2911,10 @@
         <v>9</v>
       </c>
       <c r="C202" t="n">
-        <v>30.83479466570159</v>
+        <v>26.40729487006683</v>
       </c>
       <c r="D202" t="n">
-        <v>52.16381672858296</v>
-      </c>
-      <c r="E202" t="n">
-        <v>26.95081792096906</v>
-      </c>
-      <c r="F202" t="n">
-        <v>35.95960343405779</v>
+        <v>35.30207412758625</v>
       </c>
     </row>
     <row r="203">
@@ -4139,16 +2923,10 @@
         <v>10</v>
       </c>
       <c r="C203" t="n">
-        <v>38.62866344251924</v>
+        <v>38.50933971493887</v>
       </c>
       <c r="D203" t="n">
-        <v>52.16381672858295</v>
-      </c>
-      <c r="E203" t="n">
-        <v>39.1300159953889</v>
-      </c>
-      <c r="F203" t="n">
-        <v>38.66003170703581</v>
+        <v>38.05601903599776</v>
       </c>
     </row>
     <row r="204">
@@ -4157,16 +2935,10 @@
         <v>11</v>
       </c>
       <c r="C204" t="n">
-        <v>49.23111215135965</v>
+        <v>43.22134653869729</v>
       </c>
       <c r="D204" t="n">
-        <v>58.18271865880406</v>
-      </c>
-      <c r="E204" t="n">
-        <v>44.19919759900775</v>
-      </c>
-      <c r="F204" t="n">
-        <v>51.51746153082098</v>
+        <v>50.60973672489271</v>
       </c>
     </row>
     <row r="205">
@@ -4175,16 +2947,10 @@
         <v>12</v>
       </c>
       <c r="C205" t="n">
-        <v>31.77637138842533</v>
+        <v>29.08068336047307</v>
       </c>
       <c r="D205" t="n">
-        <v>30.09450965110555</v>
-      </c>
-      <c r="E205" t="n">
-        <v>29.45260781637438</v>
-      </c>
-      <c r="F205" t="n">
-        <v>21.53390591303053</v>
+        <v>21.20358817710888</v>
       </c>
     </row>
     <row r="206">
@@ -4195,16 +2961,10 @@
         <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>20.20892329007264</v>
+        <v>19.96216993900025</v>
       </c>
       <c r="D206" t="n">
-        <v>48.15121544176888</v>
-      </c>
-      <c r="E206" t="n">
-        <v>20.35784811978984</v>
-      </c>
-      <c r="F206" t="n">
-        <v>35.64491351708252</v>
+        <v>34.94756934064561</v>
       </c>
     </row>
     <row r="207">
@@ -4213,16 +2973,10 @@
         <v>2</v>
       </c>
       <c r="C207" t="n">
-        <v>20.19992978959011</v>
+        <v>19.08257016753262</v>
       </c>
       <c r="D207" t="n">
-        <v>30.09450965110555</v>
-      </c>
-      <c r="E207" t="n">
-        <v>19.457309820639</v>
-      </c>
-      <c r="F207" t="n">
-        <v>29.90329453291903</v>
+        <v>29.44633198963036</v>
       </c>
     </row>
     <row r="208">
@@ -4231,16 +2985,10 @@
         <v>3</v>
       </c>
       <c r="C208" t="n">
-        <v>25.59179202179865</v>
+        <v>37.34877209874873</v>
       </c>
       <c r="D208" t="n">
-        <v>74.23312380606033</v>
-      </c>
-      <c r="E208" t="n">
-        <v>38.04673140293878</v>
-      </c>
-      <c r="F208" t="n">
-        <v>82.5557642001809</v>
+        <v>81.18586019652231</v>
       </c>
     </row>
     <row r="209">
@@ -4249,16 +2997,10 @@
         <v>4</v>
       </c>
       <c r="C209" t="n">
-        <v>52.80421419569731</v>
+        <v>33.23107345279784</v>
       </c>
       <c r="D209" t="n">
-        <v>56.17641801539703</v>
-      </c>
-      <c r="E209" t="n">
-        <v>34.24386397541815</v>
-      </c>
-      <c r="F209" t="n">
-        <v>34.47741449947279</v>
+        <v>33.75643143032239</v>
       </c>
     </row>
     <row r="210">
@@ -4267,16 +3009,10 @@
         <v>5</v>
       </c>
       <c r="C210" t="n">
-        <v>20.79104021664241</v>
+        <v>34.76485471694954</v>
       </c>
       <c r="D210" t="n">
-        <v>42.80108039268345</v>
-      </c>
-      <c r="E210" t="n">
-        <v>35.25623785671863</v>
-      </c>
-      <c r="F210" t="n">
-        <v>48.53591980151671</v>
+        <v>47.82902692964046</v>
       </c>
     </row>
     <row r="211">
@@ -4285,16 +3021,10 @@
         <v>6</v>
       </c>
       <c r="C211" t="n">
-        <v>47.75478731282288</v>
+        <v>57.31158186062047</v>
       </c>
       <c r="D211" t="n">
-        <v>70.6217826479277</v>
-      </c>
-      <c r="E211" t="n">
-        <v>58.44023820255501</v>
-      </c>
-      <c r="F211" t="n">
-        <v>75.39475347842752</v>
+        <v>74.19331450189161</v>
       </c>
     </row>
     <row r="212">
@@ -4303,16 +3033,10 @@
         <v>7</v>
       </c>
       <c r="C212" t="n">
-        <v>42.88554900534606</v>
+        <v>30.18613228090556</v>
       </c>
       <c r="D212" t="n">
-        <v>34.10711093791962</v>
-      </c>
-      <c r="E212" t="n">
-        <v>30.95185675015236</v>
-      </c>
-      <c r="F212" t="n">
-        <v>31.5761624732249</v>
+        <v>31.07542842297135</v>
       </c>
     </row>
     <row r="213">
@@ -4321,16 +3045,10 @@
         <v>8</v>
       </c>
       <c r="C213" t="n">
-        <v>111.9406865882606</v>
+        <v>55.93459591241685</v>
       </c>
       <c r="D213" t="n">
-        <v>44.1386141549548</v>
-      </c>
-      <c r="E213" t="n">
-        <v>56.72253940690019</v>
-      </c>
-      <c r="F213" t="n">
-        <v>39.30191787788328</v>
+        <v>38.73628517693858</v>
       </c>
     </row>
     <row r="214">
@@ -4339,16 +3057,10 @@
         <v>9</v>
       </c>
       <c r="C214" t="n">
-        <v>40.80389614855539</v>
+        <v>49.23194940599706</v>
       </c>
       <c r="D214" t="n">
-        <v>44.1386141549548</v>
-      </c>
-      <c r="E214" t="n">
-        <v>50.03381036749005</v>
-      </c>
-      <c r="F214" t="n">
-        <v>52.52089103206772</v>
+        <v>51.70102328759803</v>
       </c>
     </row>
     <row r="215">
@@ -4357,16 +3069,10 @@
         <v>10</v>
       </c>
       <c r="C215" t="n">
-        <v>23.02431438779932</v>
+        <v>32.99726618097755</v>
       </c>
       <c r="D215" t="n">
-        <v>22.0693070774774</v>
-      </c>
-      <c r="E215" t="n">
-        <v>33.43229418838748</v>
-      </c>
-      <c r="F215" t="n">
-        <v>31.02286864908899</v>
+        <v>30.63568748903804</v>
       </c>
     </row>
     <row r="216">
@@ -4375,16 +3081,10 @@
         <v>11</v>
       </c>
       <c r="C216" t="n">
-        <v>58.16968966476938</v>
+        <v>62.55493134714865</v>
       </c>
       <c r="D216" t="n">
-        <v>52.16381672858295</v>
-      </c>
-      <c r="E216" t="n">
-        <v>63.52859722993467</v>
-      </c>
-      <c r="F216" t="n">
-        <v>76.78812361020434</v>
+        <v>75.84678413479475</v>
       </c>
     </row>
     <row r="217">
@@ -4393,16 +3093,10 @@
         <v>12</v>
       </c>
       <c r="C217" t="n">
-        <v>36.05706706803751</v>
+        <v>38.00920861171814</v>
       </c>
       <c r="D217" t="n">
-        <v>46.14491479836184</v>
-      </c>
-      <c r="E217" t="n">
-        <v>38.68610384389938</v>
-      </c>
-      <c r="F217" t="n">
-        <v>47.96051006462609</v>
+        <v>47.2025043663146</v>
       </c>
     </row>
     <row r="218">
@@ -4413,16 +3107,10 @@
         <v>1</v>
       </c>
       <c r="C218" t="n">
-        <v>36.3680985402904</v>
+        <v>45.60817409897562</v>
       </c>
       <c r="D218" t="n">
-        <v>44.13861415495481</v>
-      </c>
-      <c r="E218" t="n">
-        <v>46.34829291954842</v>
-      </c>
-      <c r="F218" t="n">
-        <v>49.01223259033869</v>
+        <v>48.26915144709433</v>
       </c>
     </row>
     <row r="219">
@@ -4431,16 +3119,10 @@
         <v>2</v>
       </c>
       <c r="C219" t="n">
-        <v>25.00473997023598</v>
+        <v>23.64607001896348</v>
       </c>
       <c r="D219" t="n">
-        <v>38.1197122247337</v>
-      </c>
-      <c r="E219" t="n">
-        <v>24.15349752033753</v>
-      </c>
-      <c r="F219" t="n">
-        <v>38.16065594479029</v>
+        <v>37.56637168440559</v>
       </c>
     </row>
     <row r="220">
@@ -4449,16 +3131,10 @@
         <v>3</v>
       </c>
       <c r="C220" t="n">
-        <v>55.38220358559909</v>
+        <v>40.54963873960651</v>
       </c>
       <c r="D220" t="n">
-        <v>40.12601286814073</v>
-      </c>
-      <c r="E220" t="n">
-        <v>41.26404353055448</v>
-      </c>
-      <c r="F220" t="n">
-        <v>27.36641187889815</v>
+        <v>26.88720197769247</v>
       </c>
     </row>
     <row r="221">
@@ -4467,16 +3143,10 @@
         <v>4</v>
       </c>
       <c r="C221" t="n">
-        <v>32.92149965578233</v>
+        <v>40.60817880523949</v>
       </c>
       <c r="D221" t="n">
-        <v>50.15751608517591</v>
-      </c>
-      <c r="E221" t="n">
-        <v>41.41749366997337</v>
-      </c>
-      <c r="F221" t="n">
-        <v>51.77717849611521</v>
+        <v>50.80158250038073</v>
       </c>
     </row>
     <row r="222">
@@ -4485,16 +3155,10 @@
         <v>5</v>
       </c>
       <c r="C222" t="n">
-        <v>23.28341542571329</v>
+        <v>31.9463089787077</v>
       </c>
       <c r="D222" t="n">
-        <v>64.20162058902517</v>
-      </c>
-      <c r="E222" t="n">
-        <v>32.58163019600931</v>
-      </c>
-      <c r="F222" t="n">
-        <v>74.05513406230854</v>
+        <v>72.90185547606097</v>
       </c>
     </row>
     <row r="223">
@@ -4503,16 +3167,10 @@
         <v>6</v>
       </c>
       <c r="C223" t="n">
-        <v>27.11659234335397</v>
+        <v>49.99527668899626</v>
       </c>
       <c r="D223" t="n">
-        <v>23.54059421597589</v>
-      </c>
-      <c r="E223" t="n">
-        <v>50.54948774367036</v>
-      </c>
-      <c r="F223" t="n">
-        <v>42.73924303123574</v>
+        <v>42.29908801477206</v>
       </c>
     </row>
     <row r="224">
@@ -4521,16 +3179,10 @@
         <v>7</v>
       </c>
       <c r="C224" t="n">
-        <v>64.74890484397153</v>
+        <v>61.19549839417525</v>
       </c>
       <c r="D224" t="n">
-        <v>38.5209723534151</v>
-      </c>
-      <c r="E224" t="n">
-        <v>62.03184417154582</v>
-      </c>
-      <c r="F224" t="n">
-        <v>40.1318224254357</v>
+        <v>39.55183823472203</v>
       </c>
     </row>
     <row r="225">
@@ -4539,16 +3191,10 @@
         <v>8</v>
       </c>
       <c r="C225" t="n">
-        <v>36.50564459863593</v>
+        <v>61.98865155651815</v>
       </c>
       <c r="D225" t="n">
-        <v>104.8626469620744</v>
-      </c>
-      <c r="E225" t="n">
-        <v>63.11494898587417</v>
-      </c>
-      <c r="F225" t="n">
-        <v>125.6149266014509</v>
+        <v>123.766267333394</v>
       </c>
     </row>
     <row r="226">
@@ -4557,16 +3203,10 @@
         <v>9</v>
       </c>
       <c r="C226" t="n">
-        <v>29.23546815741061</v>
+        <v>42.13204284628969</v>
       </c>
       <c r="D226" t="n">
-        <v>49.22124245158597</v>
-      </c>
-      <c r="E226" t="n">
-        <v>42.92232649986693</v>
-      </c>
-      <c r="F226" t="n">
-        <v>41.75140625087851</v>
+        <v>40.99245318396859</v>
       </c>
     </row>
     <row r="227">
@@ -4575,16 +3215,10 @@
         <v>10</v>
       </c>
       <c r="C227" t="n">
-        <v>64.24915437316108</v>
+        <v>58.42255988817914</v>
       </c>
       <c r="D227" t="n">
-        <v>81.32205274609854</v>
-      </c>
-      <c r="E227" t="n">
-        <v>59.20997766297413</v>
-      </c>
-      <c r="F227" t="n">
-        <v>84.69978548541766</v>
+        <v>83.36776410630154</v>
       </c>
     </row>
     <row r="228">
@@ -4593,16 +3227,10 @@
         <v>11</v>
       </c>
       <c r="C228" t="n">
-        <v>49.74978237520434</v>
+        <v>50.15317099484027</v>
       </c>
       <c r="D228" t="n">
-        <v>109.1427550013428</v>
-      </c>
-      <c r="E228" t="n">
-        <v>51.21517725655422</v>
-      </c>
-      <c r="F228" t="n">
-        <v>92.50992622117256</v>
+        <v>90.86314641748636</v>
       </c>
     </row>
     <row r="229">
@@ -4611,16 +3239,10 @@
         <v>12</v>
       </c>
       <c r="C229" t="n">
-        <v>40.65552426710113</v>
+        <v>30.19957749294908</v>
       </c>
       <c r="D229" t="n">
-        <v>68.48172862829352</v>
-      </c>
-      <c r="E229" t="n">
-        <v>30.98451892063725</v>
-      </c>
-      <c r="F229" t="n">
-        <v>58.12873263295334</v>
+        <v>57.09595658376384</v>
       </c>
     </row>
     <row r="230">
@@ -4631,16 +3253,10 @@
         <v>1</v>
       </c>
       <c r="C230" t="n">
-        <v>53.71523401166639</v>
+        <v>44.84006784240049</v>
       </c>
       <c r="D230" t="n">
-        <v>72.76183666756185</v>
-      </c>
-      <c r="E230" t="n">
-        <v>45.8473352489707</v>
-      </c>
-      <c r="F230" t="n">
-        <v>55.92415384147064</v>
+        <v>54.85922392472854</v>
       </c>
     </row>
     <row r="231">
@@ -4649,16 +3265,10 @@
         <v>2</v>
       </c>
       <c r="C231" t="n">
-        <v>22.03924114544279</v>
+        <v>20.8105887637867</v>
       </c>
       <c r="D231" t="n">
-        <v>27.82070225524424</v>
-      </c>
-      <c r="E231" t="n">
-        <v>21.11017556873563</v>
-      </c>
-      <c r="F231" t="n">
-        <v>32.87162711484394</v>
+        <v>32.42420788270919</v>
       </c>
     </row>
     <row r="232">
@@ -4667,16 +3277,10 @@
         <v>3</v>
       </c>
       <c r="C232" t="n">
-        <v>41.50570637159151</v>
+        <v>47.49774784611647</v>
       </c>
       <c r="D232" t="n">
-        <v>85.60216078536689</v>
-      </c>
-      <c r="E232" t="n">
-        <v>48.27488343662868</v>
-      </c>
-      <c r="F232" t="n">
-        <v>89.59968681467181</v>
+        <v>88.12158850060419</v>
       </c>
     </row>
     <row r="233">
@@ -4685,16 +3289,10 @@
         <v>4</v>
       </c>
       <c r="C233" t="n">
-        <v>26.66965677213716</v>
+        <v>47.31379479756685</v>
       </c>
       <c r="D233" t="n">
-        <v>38.5209723534151</v>
-      </c>
-      <c r="E233" t="n">
-        <v>48.00966701159552</v>
-      </c>
-      <c r="F233" t="n">
-        <v>43.67704893769855</v>
+        <v>42.95298910911717</v>
       </c>
     </row>
     <row r="234">
@@ -4703,16 +3301,10 @@
         <v>5</v>
       </c>
       <c r="C234" t="n">
-        <v>34.15066515432447</v>
+        <v>26.35199071280885</v>
       </c>
       <c r="D234" t="n">
-        <v>49.22124245158596</v>
-      </c>
-      <c r="E234" t="n">
-        <v>26.92959663356971</v>
-      </c>
-      <c r="F234" t="n">
-        <v>51.28307050147624</v>
+        <v>50.44633300071822</v>
       </c>
     </row>
     <row r="235">
@@ -4721,16 +3313,10 @@
         <v>6</v>
       </c>
       <c r="C235" t="n">
-        <v>114.8193117355945</v>
+        <v>82.44762201354595</v>
       </c>
       <c r="D235" t="n">
-        <v>120.3780386044222</v>
-      </c>
-      <c r="E235" t="n">
-        <v>84.5504499529664</v>
-      </c>
-      <c r="F235" t="n">
-        <v>88.25708529207321</v>
+        <v>86.6625649908228</v>
       </c>
     </row>
     <row r="236">
@@ -4739,16 +3325,10 @@
         <v>7</v>
       </c>
       <c r="C236" t="n">
-        <v>62.76985845307244</v>
+        <v>65.99873181766583</v>
       </c>
       <c r="D236" t="n">
-        <v>67.76837728841546</v>
-      </c>
-      <c r="E236" t="n">
-        <v>67.0118802559807</v>
-      </c>
-      <c r="F236" t="n">
-        <v>81.76408276492448</v>
+        <v>80.72650378254687</v>
       </c>
     </row>
     <row r="237">
@@ -4757,16 +3337,10 @@
         <v>8</v>
       </c>
       <c r="C237" t="n">
-        <v>44.78174625176469</v>
+        <v>43.97772443412924</v>
       </c>
       <c r="D237" t="n">
-        <v>62.41824223933003</v>
-      </c>
-      <c r="E237" t="n">
-        <v>44.59234179130746</v>
-      </c>
-      <c r="F237" t="n">
-        <v>59.93664037531032</v>
+        <v>59.08904062236101</v>
       </c>
     </row>
     <row r="238">
@@ -4775,16 +3349,10 @@
         <v>9</v>
       </c>
       <c r="C238" t="n">
-        <v>56.29852085989656</v>
+        <v>56.98880478703249</v>
       </c>
       <c r="D238" t="n">
-        <v>67.76837728841546</v>
-      </c>
-      <c r="E238" t="n">
-        <v>57.92187639318439</v>
-      </c>
-      <c r="F238" t="n">
-        <v>66.96356723606696</v>
+        <v>66.13325106819333</v>
       </c>
     </row>
     <row r="239">
@@ -4793,16 +3361,10 @@
         <v>10</v>
       </c>
       <c r="C239" t="n">
-        <v>112.2270670854799</v>
+        <v>139.4479209542289</v>
       </c>
       <c r="D239" t="n">
-        <v>153.3705380737823</v>
-      </c>
-      <c r="E239" t="n">
-        <v>141.386055318889</v>
-      </c>
-      <c r="F239" t="n">
-        <v>155.6257276431706</v>
+        <v>153.5104793662142</v>
       </c>
     </row>
     <row r="240">
@@ -4811,16 +3373,10 @@
         <v>11</v>
       </c>
       <c r="C240" t="n">
-        <v>111.6913987583619</v>
+        <v>124.5316393783966</v>
       </c>
       <c r="D240" t="n">
-        <v>194.3882401167706</v>
-      </c>
-      <c r="E240" t="n">
-        <v>126.7665538904813</v>
-      </c>
-      <c r="F240" t="n">
-        <v>183.7105564859246</v>
+        <v>180.6748462920101</v>
       </c>
     </row>
     <row r="241">
@@ -4829,16 +3385,10 @@
         <v>12</v>
       </c>
       <c r="C241" t="n">
-        <v>118.8104810159527</v>
+        <v>115.9592840552713</v>
       </c>
       <c r="D241" t="n">
-        <v>156.9372947731726</v>
-      </c>
-      <c r="E241" t="n">
-        <v>118.0524219037546</v>
-      </c>
-      <c r="F241" t="n">
-        <v>137.2537403967539</v>
+        <v>135.1766958781097</v>
       </c>
     </row>
     <row r="242">
@@ -4849,16 +3399,10 @@
         <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>120.6124018169352</v>
+        <v>113.8204266140773</v>
       </c>
       <c r="D242" t="n">
-        <v>133.7533762271358</v>
-      </c>
-      <c r="E242" t="n">
-        <v>115.7261222546993</v>
-      </c>
-      <c r="F242" t="n">
-        <v>131.5232369895994</v>
+        <v>129.4612216797757</v>
       </c>
     </row>
     <row r="243">
@@ -4867,16 +3411,10 @@
         <v>2</v>
       </c>
       <c r="C243" t="n">
-        <v>73.38190616774392</v>
+        <v>84.80294291259671</v>
       </c>
       <c r="D243" t="n">
-        <v>114.1362143804892</v>
-      </c>
-      <c r="E243" t="n">
-        <v>85.93022286087304</v>
-      </c>
-      <c r="F243" t="n">
-        <v>114.9866297958559</v>
+        <v>113.3029298183653</v>
       </c>
     </row>
     <row r="244">
@@ -4885,16 +3423,10 @@
         <v>3</v>
       </c>
       <c r="C244" t="n">
-        <v>53.62536483493471</v>
+        <v>55.62433698785721</v>
       </c>
       <c r="D244" t="n">
-        <v>80.25202573628147</v>
-      </c>
-      <c r="E244" t="n">
-        <v>56.67941279110599</v>
-      </c>
-      <c r="F244" t="n">
-        <v>66.79881596086051</v>
+        <v>65.63808929678409</v>
       </c>
     </row>
     <row r="245">
@@ -4903,16 +3435,10 @@
         <v>4</v>
       </c>
       <c r="C245" t="n">
-        <v>79.0466640680112</v>
+        <v>97.45235217806339</v>
       </c>
       <c r="D245" t="n">
-        <v>133.7533762271358</v>
-      </c>
-      <c r="E245" t="n">
-        <v>98.96497412160062</v>
-      </c>
-      <c r="F245" t="n">
-        <v>135.4062819444073</v>
+        <v>133.4725936102557</v>
       </c>
     </row>
     <row r="246">
@@ -4921,16 +3447,10 @@
         <v>5</v>
       </c>
       <c r="C246" t="n">
-        <v>102.2054120717606</v>
+        <v>122.0349559716999</v>
       </c>
       <c r="D246" t="n">
-        <v>128.4032411780503</v>
-      </c>
-      <c r="E246" t="n">
-        <v>123.9892747146407</v>
-      </c>
-      <c r="F246" t="n">
-        <v>114.0044015398416</v>
+        <v>112.2821755185945</v>
       </c>
     </row>
     <row r="247">
@@ -4939,16 +3459,10 @@
         <v>6</v>
       </c>
       <c r="C247" t="n">
-        <v>134.3780858792898</v>
+        <v>92.77222265779669</v>
       </c>
       <c r="D247" t="n">
-        <v>101.6525659326232</v>
-      </c>
-      <c r="E247" t="n">
-        <v>94.18324162467783</v>
-      </c>
-      <c r="F247" t="n">
-        <v>86.71187655930405</v>
+        <v>85.40854386187299</v>
       </c>
     </row>
     <row r="248">
@@ -4957,16 +3471,10 @@
         <v>7</v>
       </c>
       <c r="C248" t="n">
-        <v>154.1142357967073</v>
+        <v>166.2246270625201</v>
       </c>
       <c r="D248" t="n">
-        <v>162.2874298222581</v>
-      </c>
-      <c r="E248" t="n">
-        <v>168.8493053856841</v>
-      </c>
-      <c r="F248" t="n">
-        <v>158.1205432391612</v>
+        <v>155.8699817956685</v>
       </c>
     </row>
     <row r="249">
@@ -4975,16 +3483,10 @@
         <v>8</v>
       </c>
       <c r="C249" t="n">
-        <v>115.4859567306171</v>
+        <v>101.5905066077405</v>
       </c>
       <c r="D249" t="n">
-        <v>88.74929904953478</v>
-      </c>
-      <c r="E249" t="n">
-        <v>103.1680034797265</v>
-      </c>
-      <c r="F249" t="n">
-        <v>76.11499518639329</v>
+        <v>74.909367694983</v>
       </c>
     </row>
     <row r="250">
@@ -4993,16 +3495,10 @@
         <v>9</v>
       </c>
       <c r="C250" t="n">
-        <v>143.774354892447</v>
+        <v>113.7272352388091</v>
       </c>
       <c r="D250" t="n">
-        <v>86.86101609103405</v>
-      </c>
-      <c r="E250" t="n">
-        <v>115.951287238845</v>
-      </c>
-      <c r="F250" t="n">
-        <v>80.36579221018853</v>
+        <v>79.16480515126102</v>
       </c>
     </row>
     <row r="251">
@@ -5011,16 +3507,10 @@
         <v>10</v>
       </c>
       <c r="C251" t="n">
-        <v>109.2538830123081</v>
+        <v>95.76468270534605</v>
       </c>
       <c r="D251" t="n">
-        <v>162.3923344310637</v>
-      </c>
-      <c r="E251" t="n">
-        <v>97.65916133593031</v>
-      </c>
-      <c r="F251" t="n">
-        <v>141.2465819383972</v>
+        <v>138.7500328785829</v>
       </c>
     </row>
     <row r="252">
@@ -5029,16 +3519,10 @@
         <v>11</v>
       </c>
       <c r="C252" t="n">
-        <v>119.4613749247866</v>
+        <v>117.670634292232</v>
       </c>
       <c r="D252" t="n">
-        <v>145.397787804557</v>
-      </c>
-      <c r="E252" t="n">
-        <v>119.9877207831957</v>
-      </c>
-      <c r="F252" t="n">
-        <v>122.3620277541498</v>
+        <v>120.2162482764924</v>
       </c>
     </row>
     <row r="253">
@@ -5047,16 +3531,10 @@
         <v>12</v>
       </c>
       <c r="C253" t="n">
-        <v>160.0712511603124</v>
+        <v>164.0923332414038</v>
       </c>
       <c r="D253" t="n">
-        <v>154.8392025970607</v>
-      </c>
-      <c r="E253" t="n">
-        <v>166.6304330924609</v>
-      </c>
-      <c r="F253" t="n">
-        <v>131.4889125313171</v>
+        <v>129.48758452592</v>
       </c>
     </row>
     <row r="254">
@@ -5067,16 +3545,10 @@
         <v>1</v>
       </c>
       <c r="C254" t="n">
-        <v>193.0168616856326</v>
+        <v>126.7416294580242</v>
       </c>
       <c r="D254" t="n">
-        <v>156.7274855555614</v>
-      </c>
-      <c r="E254" t="n">
-        <v>128.7549180696791</v>
-      </c>
-      <c r="F254" t="n">
-        <v>125.0174538350642</v>
+        <v>122.9098957098028</v>
       </c>
     </row>
     <row r="255">
@@ -5085,16 +3557,10 @@
         <v>2</v>
       </c>
       <c r="C255" t="n">
-        <v>99.5079832709667</v>
+        <v>92.48472972499725</v>
       </c>
       <c r="D255" t="n">
-        <v>123.0531061289649</v>
-      </c>
-      <c r="E255" t="n">
-        <v>94.47996557970373</v>
-      </c>
-      <c r="F255" t="n">
-        <v>111.6743965847714</v>
+        <v>109.8249344028735</v>
       </c>
     </row>
     <row r="256">
@@ -5103,16 +3569,10 @@
         <v>3</v>
       </c>
       <c r="C256" t="n">
-        <v>102.6097021455881</v>
+        <v>119.1145460054358</v>
       </c>
       <c r="D256" t="n">
-        <v>142.6702679756115</v>
-      </c>
-      <c r="E256" t="n">
-        <v>120.5821599232215</v>
-      </c>
-      <c r="F256" t="n">
-        <v>148.0573083733317</v>
+        <v>146.0997549090081</v>
       </c>
     </row>
     <row r="257">
@@ -5121,16 +3581,10 @@
         <v>4</v>
       </c>
       <c r="C257" t="n">
-        <v>75.58991215028713</v>
+        <v>96.03526674818012</v>
       </c>
       <c r="D257" t="n">
-        <v>137.320132926526</v>
-      </c>
-      <c r="E257" t="n">
-        <v>97.30702647591531</v>
-      </c>
-      <c r="F257" t="n">
-        <v>144.4141130726247</v>
+        <v>142.4064475003586</v>
       </c>
     </row>
     <row r="258">
@@ -5139,16 +3593,10 @@
         <v>5</v>
       </c>
       <c r="C258" t="n">
-        <v>184.3498087881906</v>
+        <v>176.2701025194238</v>
       </c>
       <c r="D258" t="n">
-        <v>230.0558071106735</v>
-      </c>
-      <c r="E258" t="n">
-        <v>179.1134145382555</v>
-      </c>
-      <c r="F258" t="n">
-        <v>195.4321696695968</v>
+        <v>192.2639533914491</v>
       </c>
     </row>
     <row r="259">
@@ -5157,16 +3605,10 @@
         <v>6</v>
       </c>
       <c r="C259" t="n">
-        <v>246.5843190831176</v>
+        <v>207.4355091476076</v>
       </c>
       <c r="D259" t="n">
-        <v>183.6879700185998</v>
-      </c>
-      <c r="E259" t="n">
-        <v>211.2943803691979</v>
-      </c>
-      <c r="F259" t="n">
-        <v>186.441253797429</v>
+        <v>183.7937774768235</v>
       </c>
     </row>
     <row r="260">
@@ -5175,16 +3617,10 @@
         <v>7</v>
       </c>
       <c r="C260" t="n">
-        <v>182.1741370922028</v>
+        <v>174.6113050396935</v>
       </c>
       <c r="D260" t="n">
-        <v>230.0558071106736</v>
-      </c>
-      <c r="E260" t="n">
-        <v>177.0823362144606</v>
-      </c>
-      <c r="F260" t="n">
-        <v>222.753642147811</v>
+        <v>219.343380382626</v>
       </c>
     </row>
     <row r="261">
@@ -5193,16 +3629,10 @@
         <v>8</v>
       </c>
       <c r="C261" t="n">
-        <v>170.8860436164058</v>
+        <v>177.1205383553209</v>
       </c>
       <c r="D261" t="n">
-        <v>137.844655970554</v>
-      </c>
-      <c r="E261" t="n">
-        <v>180.1655556370018</v>
-      </c>
-      <c r="F261" t="n">
-        <v>143.8774892422005</v>
+        <v>141.7333851282627</v>
       </c>
     </row>
     <row r="262">
@@ -5211,16 +3641,10 @@
         <v>9</v>
       </c>
       <c r="C262" t="n">
-        <v>236.1053444336533</v>
+        <v>259.4147353218528</v>
       </c>
       <c r="D262" t="n">
-        <v>296.4604244846162</v>
-      </c>
-      <c r="E262" t="n">
-        <v>263.5056453250186</v>
-      </c>
-      <c r="F262" t="n">
-        <v>273.6657070392676</v>
+        <v>269.470302800813</v>
       </c>
     </row>
     <row r="263">
@@ -5229,16 +3653,10 @@
         <v>10</v>
       </c>
       <c r="C263" t="n">
-        <v>198.656224696253</v>
+        <v>216.0080036233134</v>
       </c>
       <c r="D263" t="n">
-        <v>282.8883907203921</v>
-      </c>
-      <c r="E263" t="n">
-        <v>219.4683376711676</v>
-      </c>
-      <c r="F263" t="n">
-        <v>280.741680416163</v>
+        <v>276.2591123981083</v>
       </c>
     </row>
     <row r="264">
@@ -5247,16 +3665,10 @@
         <v>11</v>
       </c>
       <c r="C264" t="n">
-        <v>191.4249289976643</v>
+        <v>182.256983795789</v>
       </c>
       <c r="D264" t="n">
-        <v>165.8541865216484</v>
-      </c>
-      <c r="E264" t="n">
-        <v>185.0340014717674</v>
-      </c>
-      <c r="F264" t="n">
-        <v>180.1578952486634</v>
+        <v>177.6948327360394</v>
       </c>
     </row>
     <row r="265">
@@ -5265,16 +3677,10 @@
         <v>12</v>
       </c>
       <c r="C265" t="n">
-        <v>335.9019465391632</v>
+        <v>290.6959420429054</v>
       </c>
       <c r="D265" t="n">
-        <v>222.9222937118929</v>
-      </c>
-      <c r="E265" t="n">
-        <v>295.162952758373</v>
-      </c>
-      <c r="F265" t="n">
-        <v>220.9211728754801</v>
+        <v>217.8076550784422</v>
       </c>
     </row>
     <row r="266">
@@ -5285,16 +3691,10 @@
         <v>1</v>
       </c>
       <c r="C266" t="n">
-        <v>271.1504804640302</v>
+        <v>270.868817867177</v>
       </c>
       <c r="D266" t="n">
-        <v>294.2574276996987</v>
-      </c>
-      <c r="E266" t="n">
-        <v>274.4269338701529</v>
-      </c>
-      <c r="F266" t="n">
-        <v>270.2887657786217</v>
+        <v>266.2156890906256</v>
       </c>
     </row>
     <row r="267">
@@ -5303,16 +3703,10 @@
         <v>2</v>
       </c>
       <c r="C267" t="n">
-        <v>155.7002486261302</v>
+        <v>161.8755125460381</v>
       </c>
       <c r="D267" t="n">
-        <v>181.275164016071</v>
-      </c>
-      <c r="E267" t="n">
-        <v>164.0513641872539</v>
-      </c>
-      <c r="F267" t="n">
-        <v>166.2987548502065</v>
+        <v>163.8805781793318</v>
       </c>
     </row>
     <row r="268">
@@ -5321,16 +3715,10 @@
         <v>3</v>
       </c>
       <c r="C268" t="n">
-        <v>73.50154317635347</v>
+        <v>81.56245281452428</v>
       </c>
       <c r="D268" t="n">
-        <v>135.9563730120533</v>
-      </c>
-      <c r="E268" t="n">
-        <v>82.51860409065654</v>
-      </c>
-      <c r="F268" t="n">
-        <v>114.3021594950371</v>
+        <v>112.5778733358549</v>
       </c>
     </row>
     <row r="269">
@@ -5339,16 +3727,10 @@
         <v>4</v>
       </c>
       <c r="C269" t="n">
-        <v>63.02411862678494</v>
+        <v>59.85761523937602</v>
       </c>
       <c r="D269" t="n">
-        <v>49.93459379146402</v>
-      </c>
-      <c r="E269" t="n">
-        <v>60.57369682836886</v>
-      </c>
-      <c r="F269" t="n">
-        <v>38.43653554371762</v>
+        <v>37.84015516294834</v>
       </c>
     </row>
     <row r="270">
@@ -5357,16 +3739,10 @@
         <v>5</v>
       </c>
       <c r="C270" t="n">
-        <v>172.2581143523673</v>
+        <v>124.2442612469851</v>
       </c>
       <c r="D270" t="n">
-        <v>136.850822834501</v>
-      </c>
-      <c r="E270" t="n">
-        <v>125.9285452963074</v>
-      </c>
-      <c r="F270" t="n">
-        <v>121.0074551790865</v>
+        <v>119.2424921875777</v>
       </c>
     </row>
     <row r="271">
@@ -5375,16 +3751,10 @@
         <v>6</v>
       </c>
       <c r="C271" t="n">
-        <v>182.4212683043933</v>
+        <v>194.9890760674373</v>
       </c>
       <c r="D271" t="n">
-        <v>244.3228339082347</v>
-      </c>
-      <c r="E271" t="n">
-        <v>197.2051389815762</v>
-      </c>
-      <c r="F271" t="n">
-        <v>236.7111066866671</v>
+        <v>233.4516982791318</v>
       </c>
     </row>
     <row r="272">
@@ -5393,16 +3763,10 @@
         <v>7</v>
       </c>
       <c r="C272" t="n">
-        <v>245.3302242245163</v>
+        <v>144.1507764434453</v>
       </c>
       <c r="D272" t="n">
-        <v>170.6411494603037</v>
-      </c>
-      <c r="E272" t="n">
-        <v>146.8552694405883</v>
-      </c>
-      <c r="F272" t="n">
-        <v>139.4569568129529</v>
+        <v>137.376535920378</v>
       </c>
     </row>
     <row r="273">
@@ -5411,16 +3775,10 @@
         <v>8</v>
       </c>
       <c r="C273" t="n">
-        <v>132.4693913066073</v>
+        <v>129.3906279162975</v>
       </c>
       <c r="D273" t="n">
-        <v>76.02823490805612</v>
-      </c>
-      <c r="E273" t="n">
-        <v>131.5239529176587</v>
-      </c>
-      <c r="F273" t="n">
-        <v>84.11004639823688</v>
+        <v>83.07846477080514</v>
       </c>
     </row>
     <row r="274">
@@ -5429,16 +3787,10 @@
         <v>9</v>
       </c>
       <c r="C274" t="n">
-        <v>215.4666292127478</v>
+        <v>206.017254042364</v>
       </c>
       <c r="D274" t="n">
-        <v>168.9516331290136</v>
-      </c>
-      <c r="E274" t="n">
-        <v>208.4737601108127</v>
-      </c>
-      <c r="F274" t="n">
-        <v>154.3773785723914</v>
+        <v>152.4313506648215</v>
       </c>
     </row>
     <row r="275">
@@ -5447,16 +3799,10 @@
         <v>10</v>
       </c>
       <c r="C275" t="n">
-        <v>139.2657999516476</v>
+        <v>136.6036376126702</v>
       </c>
       <c r="D275" t="n">
-        <v>126.7137248467602</v>
-      </c>
-      <c r="E275" t="n">
-        <v>138.2797502118487</v>
-      </c>
-      <c r="F275" t="n">
-        <v>139.3946327857495</v>
+        <v>137.7944122964202</v>
       </c>
     </row>
     <row r="276">
@@ -5465,16 +3811,10 @@
         <v>11</v>
       </c>
       <c r="C276" t="n">
-        <v>141.686558254269</v>
+        <v>120.7159294258663</v>
       </c>
       <c r="D276" t="n">
-        <v>107.0027009817086</v>
-      </c>
-      <c r="E276" t="n">
-        <v>123.0797625990206</v>
-      </c>
-      <c r="F276" t="n">
-        <v>103.5750507257645</v>
+        <v>102.0974224759248</v>
       </c>
     </row>
     <row r="277">
@@ -5483,16 +3823,10 @@
         <v>12</v>
       </c>
       <c r="C277" t="n">
-        <v>126.4133567113773</v>
+        <v>115.9070019504856</v>
       </c>
       <c r="D277" t="n">
-        <v>130.0927575093405</v>
-      </c>
-      <c r="E277" t="n">
-        <v>117.2436021189834</v>
-      </c>
-      <c r="F277" t="n">
-        <v>100.1214664705973</v>
+        <v>98.65949654830742</v>
       </c>
     </row>
     <row r="278">
@@ -5503,16 +3837,10 @@
         <v>1</v>
       </c>
       <c r="C278" t="n">
-        <v>147.1621213266497</v>
+        <v>118.6382097142069</v>
       </c>
       <c r="D278" t="n">
-        <v>133.4717901719208</v>
-      </c>
-      <c r="E278" t="n">
-        <v>120.3616524583437</v>
-      </c>
-      <c r="F278" t="n">
-        <v>103.882303227622</v>
+        <v>102.3813972301444</v>
       </c>
     </row>
     <row r="279">
@@ -5521,16 +3849,10 @@
         <v>2</v>
       </c>
       <c r="C279" t="n">
-        <v>134.8345283582322</v>
+        <v>137.7743509548953</v>
       </c>
       <c r="D279" t="n">
-        <v>179.0887311167544</v>
-      </c>
-      <c r="E279" t="n">
-        <v>139.7157765132081</v>
-      </c>
-      <c r="F279" t="n">
-        <v>150.6520482024949</v>
+        <v>148.4438146962055</v>
       </c>
     </row>
     <row r="280">
@@ -5539,16 +3861,10 @@
         <v>3</v>
       </c>
       <c r="C280" t="n">
-        <v>217.2073053804499</v>
+        <v>189.7967681070674</v>
       </c>
       <c r="D280" t="n">
-        <v>242.5394555585395</v>
-      </c>
-      <c r="E280" t="n">
-        <v>193.1943676132396</v>
-      </c>
-      <c r="F280" t="n">
-        <v>210.6240706664153</v>
+        <v>207.3321002906166</v>
       </c>
     </row>
     <row r="281">
@@ -5557,16 +3873,10 @@
         <v>4</v>
       </c>
       <c r="C281" t="n">
-        <v>171.6043513115525</v>
+        <v>152.0502112400519</v>
       </c>
       <c r="D281" t="n">
-        <v>222.9222937118929</v>
-      </c>
-      <c r="E281" t="n">
-        <v>154.2892061114446</v>
-      </c>
-      <c r="F281" t="n">
-        <v>199.5770992774478</v>
+        <v>196.5772241398738</v>
       </c>
     </row>
     <row r="282">
@@ -5575,16 +3885,10 @@
         <v>5</v>
       </c>
       <c r="C282" t="n">
-        <v>245.2735221269122</v>
+        <v>136.930931208437</v>
       </c>
       <c r="D282" t="n">
-        <v>190.9153454357854</v>
-      </c>
-      <c r="E282" t="n">
-        <v>139.3785685002718</v>
-      </c>
-      <c r="F282" t="n">
-        <v>141.3988770852837</v>
+        <v>138.783682713269</v>
       </c>
     </row>
     <row r="283">
@@ -5593,16 +3897,10 @@
         <v>6</v>
       </c>
       <c r="C283" t="n">
-        <v>158.9235156724293</v>
+        <v>126.2863393166747</v>
       </c>
       <c r="D283" t="n">
-        <v>168.9516331290136</v>
-      </c>
-      <c r="E283" t="n">
-        <v>128.1492819639547</v>
-      </c>
-      <c r="F283" t="n">
-        <v>138.4210724883046</v>
+        <v>136.1400464511829</v>
       </c>
     </row>
     <row r="284">
@@ -5611,16 +3909,10 @@
         <v>7</v>
       </c>
       <c r="C284" t="n">
-        <v>165.1082708238956</v>
+        <v>205.9951526818582</v>
       </c>
       <c r="D284" t="n">
-        <v>241.7002186880948</v>
-      </c>
-      <c r="E284" t="n">
-        <v>209.0980256502641</v>
-      </c>
-      <c r="F284" t="n">
-        <v>253.7878596414938</v>
+        <v>250.1393811633984</v>
       </c>
     </row>
     <row r="285">
@@ -5629,16 +3921,10 @@
         <v>8</v>
       </c>
       <c r="C285" t="n">
-        <v>145.8272654091283</v>
+        <v>164.739833551552</v>
       </c>
       <c r="D285" t="n">
-        <v>151.5871597240872</v>
-      </c>
-      <c r="E285" t="n">
-        <v>167.8637864770883</v>
-      </c>
-      <c r="F285" t="n">
-        <v>166.3468043607254</v>
+        <v>163.7606451268054</v>
       </c>
     </row>
     <row r="286">
@@ -5647,16 +3933,10 @@
         <v>9</v>
       </c>
       <c r="C286" t="n">
-        <v>248.8441642110357</v>
+        <v>225.3489336148497</v>
       </c>
       <c r="D286" t="n">
-        <v>287.1239143009181</v>
-      </c>
-      <c r="E286" t="n">
-        <v>229.012741936212</v>
-      </c>
-      <c r="F286" t="n">
-        <v>217.3031968667364</v>
+        <v>213.6285976897902</v>
       </c>
     </row>
     <row r="287">
@@ -5665,16 +3945,10 @@
         <v>10</v>
       </c>
       <c r="C287" t="n">
-        <v>368.6293803905239</v>
+        <v>320.5236722603149</v>
       </c>
       <c r="D287" t="n">
-        <v>321.0081029451258</v>
-      </c>
-      <c r="E287" t="n">
-        <v>324.8177578609354</v>
-      </c>
-      <c r="F287" t="n">
-        <v>288.7469467182507</v>
+        <v>284.3000918502259</v>
       </c>
     </row>
     <row r="288">
@@ -5683,16 +3957,10 @@
         <v>11</v>
       </c>
       <c r="C288" t="n">
-        <v>215.944287365024</v>
+        <v>223.793613825257</v>
       </c>
       <c r="D288" t="n">
-        <v>311.3778598567721</v>
-      </c>
-      <c r="E288" t="n">
-        <v>227.3257483776242</v>
-      </c>
-      <c r="F288" t="n">
-        <v>260.9344731447603</v>
+        <v>256.6519861505262</v>
       </c>
     </row>
     <row r="289">
@@ -5701,16 +3969,10 @@
         <v>12</v>
       </c>
       <c r="C289" t="n">
-        <v>174.3775386401992</v>
+        <v>165.1938051122666</v>
       </c>
       <c r="D289" t="n">
-        <v>194.2099022818011</v>
-      </c>
-      <c r="E289" t="n">
-        <v>167.6722584531599</v>
-      </c>
-      <c r="F289" t="n">
-        <v>164.6691813844503</v>
+        <v>162.1203132332987</v>
       </c>
     </row>
     <row r="290">
@@ -5721,16 +3983,10 @@
         <v>1</v>
       </c>
       <c r="C290" t="n">
-        <v>187.307761759829</v>
+        <v>198.2240333396428</v>
       </c>
       <c r="D290" t="n">
-        <v>260.185515018681</v>
-      </c>
-      <c r="E290" t="n">
-        <v>201.3818386361187</v>
-      </c>
-      <c r="F290" t="n">
-        <v>225.6314657886508</v>
+        <v>222.0888592216118</v>
       </c>
     </row>
     <row r="291">
@@ -5739,16 +3995,10 @@
         <v>2</v>
       </c>
       <c r="C291" t="n">
-        <v>304.6161843091422</v>
+        <v>266.1218713876351</v>
       </c>
       <c r="D291" t="n">
-        <v>263.2266444150032</v>
-      </c>
-      <c r="E291" t="n">
-        <v>269.9033105153774</v>
-      </c>
-      <c r="F291" t="n">
-        <v>243.5915963964785</v>
+        <v>239.9301777559635</v>
       </c>
     </row>
     <row r="292">
@@ -5757,16 +4007,10 @@
         <v>3</v>
       </c>
       <c r="C292" t="n">
-        <v>199.0341297158928</v>
+        <v>163.2491539035403</v>
       </c>
       <c r="D292" t="n">
-        <v>176.5544566198192</v>
-      </c>
-      <c r="E292" t="n">
-        <v>165.8808080166294</v>
-      </c>
-      <c r="F292" t="n">
-        <v>150.7025351071052</v>
+        <v>148.3024651789354</v>
       </c>
     </row>
     <row r="293">
@@ -5775,16 +4019,10 @@
         <v>4</v>
       </c>
       <c r="C293" t="n">
-        <v>158.2585539600531</v>
+        <v>166.4908478945636</v>
       </c>
       <c r="D293" t="n">
-        <v>195.9838944296557</v>
-      </c>
-      <c r="E293" t="n">
-        <v>168.9794382148965</v>
-      </c>
-      <c r="F293" t="n">
-        <v>177.6999078451269</v>
+        <v>175.0924405289576</v>
       </c>
     </row>
     <row r="294">
@@ -5793,16 +4031,10 @@
         <v>5</v>
       </c>
       <c r="C294" t="n">
-        <v>276.0536850875931</v>
+        <v>238.2439962143589</v>
       </c>
       <c r="D294" t="n">
-        <v>269.6468064739057</v>
-      </c>
-      <c r="E294" t="n">
-        <v>241.3039577415492</v>
-      </c>
-      <c r="F294" t="n">
-        <v>216.8535348450974</v>
+        <v>213.7762625866658</v>
       </c>
     </row>
     <row r="295">
@@ -5811,16 +4043,10 @@
         <v>6</v>
       </c>
       <c r="C295" t="n">
-        <v>258.395890687987</v>
+        <v>270.4341132780811</v>
       </c>
       <c r="D295" t="n">
-        <v>293.7224141947901</v>
-      </c>
-      <c r="E295" t="n">
-        <v>274.0864280359564</v>
-      </c>
-      <c r="F295" t="n">
-        <v>262.6718862659428</v>
+        <v>258.7924489899936</v>
       </c>
     </row>
     <row r="296">
@@ -5829,16 +4055,10 @@
         <v>7</v>
       </c>
       <c r="C296" t="n">
-        <v>557.2547335662449</v>
+        <v>369.6500274456685</v>
       </c>
       <c r="D296" t="n">
-        <v>367.5542778721691</v>
-      </c>
-      <c r="E296" t="n">
-        <v>374.9516749052196</v>
-      </c>
-      <c r="F296" t="n">
-        <v>300.0118602610617</v>
+        <v>295.4371483569232</v>
       </c>
     </row>
     <row r="297">
@@ -5847,16 +4067,10 @@
         <v>8</v>
       </c>
       <c r="C297" t="n">
-        <v>187.0478657067881</v>
+        <v>185.1174929914705</v>
       </c>
       <c r="D297" t="n">
-        <v>174.020182122884</v>
-      </c>
-      <c r="E297" t="n">
-        <v>188.3039783201021</v>
-      </c>
-      <c r="F297" t="n">
-        <v>164.8411716999765</v>
+        <v>162.4100921966755</v>
       </c>
     </row>
     <row r="298">
@@ -5865,16 +4079,10 @@
         <v>9</v>
       </c>
       <c r="C298" t="n">
-        <v>230.3640922794009</v>
+        <v>192.8414968243927</v>
       </c>
       <c r="D298" t="n">
-        <v>255.0231040064055</v>
-      </c>
-      <c r="E298" t="n">
-        <v>196.1455850484374</v>
-      </c>
-      <c r="F298" t="n">
-        <v>189.8016986712219</v>
+        <v>186.7111057368726</v>
       </c>
     </row>
     <row r="299">
@@ -5883,16 +4091,10 @@
         <v>10</v>
       </c>
       <c r="C299" t="n">
-        <v>207.5487229602764</v>
+        <v>189.1214062527911</v>
       </c>
       <c r="D299" t="n">
-        <v>272.0121293377119</v>
-      </c>
-      <c r="E299" t="n">
-        <v>192.1913615808729</v>
-      </c>
-      <c r="F299" t="n">
-        <v>202.8486935753438</v>
+        <v>199.5410436295796</v>
       </c>
     </row>
     <row r="300">
@@ -5901,16 +4103,10 @@
         <v>11</v>
       </c>
       <c r="C300" t="n">
-        <v>226.2389122429741</v>
+        <v>218.2775045001143</v>
       </c>
       <c r="D300" t="n">
-        <v>313.8745895463452</v>
-      </c>
-      <c r="E300" t="n">
-        <v>222.1218038635254</v>
-      </c>
-      <c r="F300" t="n">
-        <v>252.391171454448</v>
+        <v>248.2643444764435</v>
       </c>
     </row>
     <row r="301">
@@ -5919,16 +4115,10 @@
         <v>12</v>
       </c>
       <c r="C301" t="n">
-        <v>218.002637069908</v>
+        <v>166.7160761926297</v>
       </c>
       <c r="D301" t="n">
-        <v>187.5363127732051</v>
-      </c>
-      <c r="E301" t="n">
-        <v>169.0143702601702</v>
-      </c>
-      <c r="F301" t="n">
-        <v>162.5700735466963</v>
+        <v>160.2808107778723</v>
       </c>
     </row>
     <row r="302">
@@ -5939,16 +4129,10 @@
         <v>1</v>
       </c>
       <c r="C302" t="n">
-        <v>133.7545056274504</v>
+        <v>115.3245998789187</v>
       </c>
       <c r="D302" t="n">
-        <v>182.9746186787217</v>
-      </c>
-      <c r="E302" t="n">
-        <v>117.6137763169054</v>
-      </c>
-      <c r="F302" t="n">
-        <v>123.7534552514712</v>
+        <v>121.4163574187246</v>
       </c>
     </row>
     <row r="303">
@@ -5957,16 +4141,10 @@
         <v>2</v>
       </c>
       <c r="C303" t="n">
-        <v>173.7444265403691</v>
+        <v>155.6135422545269</v>
       </c>
       <c r="D303" t="n">
-        <v>153.7459861474024</v>
-      </c>
-      <c r="E303" t="n">
-        <v>157.7798718411513</v>
-      </c>
-      <c r="F303" t="n">
-        <v>111.0766689417314</v>
+        <v>109.4604693105656</v>
       </c>
     </row>
     <row r="304">
@@ -5975,16 +4153,10 @@
         <v>3</v>
       </c>
       <c r="C304" t="n">
-        <v>210.2141130476239</v>
+        <v>207.9021773834957</v>
       </c>
       <c r="D304" t="n">
-        <v>268.6330966751316</v>
-      </c>
-      <c r="E304" t="n">
-        <v>210.5142365494328</v>
-      </c>
-      <c r="F304" t="n">
-        <v>218.2230076558003</v>
+        <v>215.1406109176109</v>
       </c>
     </row>
     <row r="305">
@@ -5993,16 +4165,10 @@
         <v>4</v>
       </c>
       <c r="C305" t="n">
-        <v>170.02390183583</v>
+        <v>126.7794857963562</v>
       </c>
       <c r="D305" t="n">
-        <v>166.9242135314654</v>
-      </c>
-      <c r="E305" t="n">
-        <v>129.4113699231183</v>
-      </c>
-      <c r="F305" t="n">
-        <v>104.2057588411986</v>
+        <v>102.3496383174388</v>
       </c>
     </row>
     <row r="306">
@@ -6011,16 +4177,10 @@
         <v>5</v>
       </c>
       <c r="C306" t="n">
-        <v>341.9980110920473</v>
+        <v>293.3003894827702</v>
       </c>
       <c r="D306" t="n">
-        <v>298.537535738967</v>
-      </c>
-      <c r="E306" t="n">
-        <v>297.4489231942997</v>
-      </c>
-      <c r="F306" t="n">
-        <v>250.2099899592251</v>
+        <v>246.5393308870371</v>
       </c>
     </row>
     <row r="307">
@@ -6029,16 +4189,10 @@
         <v>6</v>
       </c>
       <c r="C307" t="n">
-        <v>290.6828074555276</v>
+        <v>261.3383746882276</v>
       </c>
       <c r="D307" t="n">
-        <v>255.1169660248105</v>
-      </c>
-      <c r="E307" t="n">
-        <v>265.6226204667981</v>
-      </c>
-      <c r="F307" t="n">
-        <v>191.6566506910393</v>
+        <v>188.6242425869666</v>
       </c>
     </row>
     <row r="308">
@@ -6047,16 +4201,10 @@
         <v>7</v>
       </c>
       <c r="C308" t="n">
-        <v>356.8890260663111</v>
+        <v>240.4484853329187</v>
       </c>
       <c r="D308" t="n">
-        <v>186.184699708173</v>
-      </c>
-      <c r="E308" t="n">
-        <v>244.5666123715662</v>
-      </c>
-      <c r="F308" t="n">
-        <v>133.9777291076993</v>
+        <v>131.7554029097268</v>
       </c>
     </row>
     <row r="309">
@@ -6065,16 +4213,10 @@
         <v>8</v>
       </c>
       <c r="C309" t="n">
-        <v>158.5697623309408</v>
+        <v>156.9478738238261</v>
       </c>
       <c r="D309" t="n">
-        <v>141.9193718283714</v>
-      </c>
-      <c r="E309" t="n">
-        <v>158.9034862607921</v>
-      </c>
-      <c r="F309" t="n">
-        <v>128.7329206772281</v>
+        <v>127.0424062218847</v>
       </c>
     </row>
     <row r="310">
@@ -6083,16 +4225,10 @@
         <v>9</v>
       </c>
       <c r="C310" t="n">
-        <v>305.0402202088098</v>
+        <v>271.7922516127566</v>
       </c>
       <c r="D310" t="n">
-        <v>266.4367254444545</v>
-      </c>
-      <c r="E310" t="n">
-        <v>276.1073942369184</v>
-      </c>
-      <c r="F310" t="n">
-        <v>229.3493115203862</v>
+        <v>226.2138616692979</v>
       </c>
     </row>
     <row r="311">
@@ -6101,16 +4237,10 @@
         <v>10</v>
       </c>
       <c r="C311" t="n">
-        <v>382.4358057989427</v>
+        <v>290.9560568995391</v>
       </c>
       <c r="D311" t="n">
-        <v>297.3548743070639</v>
-      </c>
-      <c r="E311" t="n">
-        <v>295.072040206237</v>
-      </c>
-      <c r="F311" t="n">
-        <v>224.0535652762679</v>
+        <v>220.5748666920553</v>
       </c>
     </row>
     <row r="312">
@@ -6119,16 +4249,10 @@
         <v>11</v>
       </c>
       <c r="C312" t="n">
-        <v>203.8525832590869</v>
+        <v>202.6489380404716</v>
       </c>
       <c r="D312" t="n">
-        <v>274.6402658530521</v>
-      </c>
-      <c r="E312" t="n">
-        <v>205.9838553619037</v>
-      </c>
-      <c r="F312" t="n">
-        <v>223.4375416482752</v>
+        <v>219.9283550526118</v>
       </c>
     </row>
     <row r="313">
@@ -6137,16 +4261,10 @@
         <v>12</v>
       </c>
       <c r="C313" t="n">
-        <v>228.5323137110483</v>
+        <v>218.3586164461203</v>
       </c>
       <c r="D313" t="n">
-        <v>180.1212133192095</v>
-      </c>
-      <c r="E313" t="n">
-        <v>221.7094511237055</v>
-      </c>
-      <c r="F313" t="n">
-        <v>148.4239268487794</v>
+        <v>146.3026834717286</v>
       </c>
     </row>
     <row r="314">
@@ -6157,16 +4275,10 @@
         <v>1</v>
       </c>
       <c r="C314" t="n">
-        <v>251.4437159178537</v>
+        <v>155.0397417443361</v>
       </c>
       <c r="D314" t="n">
-        <v>195.9838944296557</v>
-      </c>
-      <c r="E314" t="n">
-        <v>157.3268330086926</v>
-      </c>
-      <c r="F314" t="n">
-        <v>158.8808748118088</v>
+        <v>156.5272444123306</v>
       </c>
     </row>
     <row r="315">
@@ -6175,16 +4287,10 @@
         <v>2</v>
       </c>
       <c r="C315" t="n">
-        <v>268.7539319001914</v>
+        <v>227.1669516754259</v>
       </c>
       <c r="D315" t="n">
-        <v>285.1307267336118</v>
-      </c>
-      <c r="E315" t="n">
-        <v>231.2741975066793</v>
-      </c>
-      <c r="F315" t="n">
-        <v>227.9221591262841</v>
+        <v>224.4075820090567</v>
       </c>
     </row>
     <row r="316">
@@ -6193,16 +4299,10 @@
         <v>3</v>
       </c>
       <c r="C316" t="n">
-        <v>358.510691779809</v>
+        <v>245.650605674469</v>
       </c>
       <c r="D316" t="n">
-        <v>328.1416163439065</v>
-      </c>
-      <c r="E316" t="n">
-        <v>249.9128599887938</v>
-      </c>
-      <c r="F316" t="n">
-        <v>250.6750498757993</v>
+        <v>246.6470633507702</v>
       </c>
     </row>
     <row r="317">
@@ -6211,16 +4311,10 @@
         <v>4</v>
       </c>
       <c r="C317" t="n">
-        <v>311.0960416849387</v>
+        <v>179.7562053524194</v>
       </c>
       <c r="D317" t="n">
-        <v>197.954996816161</v>
-      </c>
-      <c r="E317" t="n">
-        <v>182.5840070925255</v>
-      </c>
-      <c r="F317" t="n">
-        <v>121.1575905844991</v>
+        <v>118.9540411666981</v>
       </c>
     </row>
     <row r="318">
@@ -6229,16 +4323,10 @@
         <v>5</v>
       </c>
       <c r="C318" t="n">
-        <v>273.3952608663421</v>
+        <v>251.0539925900486</v>
       </c>
       <c r="D318" t="n">
-        <v>221.1389153621978</v>
-      </c>
-      <c r="E318" t="n">
-        <v>255.1374878847601</v>
-      </c>
-      <c r="F318" t="n">
-        <v>156.8275278040937</v>
+        <v>154.2470050939599</v>
       </c>
     </row>
     <row r="319">
@@ -6247,16 +4335,10 @@
         <v>6</v>
       </c>
       <c r="C319" t="n">
-        <v>214.3599892696402</v>
+        <v>159.8212219347587</v>
       </c>
       <c r="D319" t="n">
-        <v>197.954996816161</v>
-      </c>
-      <c r="E319" t="n">
-        <v>163.181005251543</v>
-      </c>
-      <c r="F319" t="n">
-        <v>137.6712690258068</v>
+        <v>135.2626268453124</v>
       </c>
     </row>
     <row r="320">
@@ -6265,16 +4347,10 @@
         <v>7</v>
       </c>
       <c r="C320" t="n">
-        <v>238.5678149276867</v>
+        <v>209.1107507882005</v>
       </c>
       <c r="D320" t="n">
-        <v>233.1532537180388</v>
-      </c>
-      <c r="E320" t="n">
-        <v>212.2950887469938</v>
-      </c>
-      <c r="F320" t="n">
-        <v>195.1271412439833</v>
+        <v>192.3331603983464</v>
       </c>
     </row>
     <row r="321">
@@ -6283,16 +4359,10 @@
         <v>8</v>
       </c>
       <c r="C321" t="n">
-        <v>186.6024281125474</v>
+        <v>160.1682212857143</v>
       </c>
       <c r="D321" t="n">
-        <v>120.8501093440474</v>
-      </c>
-      <c r="E321" t="n">
-        <v>162.3761886963973</v>
-      </c>
-      <c r="F321" t="n">
-        <v>77.66073314414619</v>
+        <v>76.44450807526621</v>
       </c>
     </row>
     <row r="322">
@@ -6301,16 +4371,10 @@
         <v>9</v>
       </c>
       <c r="C322" t="n">
-        <v>237.6288782176357</v>
+        <v>196.9792737518387</v>
       </c>
       <c r="D322" t="n">
-        <v>190.8214834173803</v>
-      </c>
-      <c r="E322" t="n">
-        <v>200.7153148271273</v>
-      </c>
-      <c r="F322" t="n">
-        <v>142.4776274770542</v>
+        <v>140.2297980557105</v>
       </c>
     </row>
     <row r="323">
@@ -6319,16 +4383,10 @@
         <v>10</v>
       </c>
       <c r="C323" t="n">
-        <v>278.6854103778763</v>
+        <v>183.2294420396666</v>
       </c>
       <c r="D323" t="n">
-        <v>173.344375590368</v>
-      </c>
-      <c r="E323" t="n">
-        <v>182.899063817537</v>
-      </c>
-      <c r="F323" t="n">
-        <v>157.4035869343489</v>
+        <v>156.4435407124267</v>
       </c>
     </row>
     <row r="324">
@@ -6337,16 +4395,10 @@
         <v>11</v>
       </c>
       <c r="C324" t="n">
-        <v>257.8623770145184</v>
+        <v>249.4123301345455</v>
       </c>
       <c r="D324" t="n">
-        <v>208.6552669143318</v>
-      </c>
-      <c r="E324" t="n">
-        <v>252.7050468640566</v>
-      </c>
-      <c r="F324" t="n">
-        <v>175.9444238871138</v>
+        <v>173.5795339343932</v>
       </c>
     </row>
     <row r="325">
@@ -6355,16 +4407,10 @@
         <v>12</v>
       </c>
       <c r="C325" t="n">
-        <v>160.9342928153852</v>
+        <v>161.6295144349117</v>
       </c>
       <c r="D325" t="n">
-        <v>128.4032411780503</v>
-      </c>
-      <c r="E325" t="n">
-        <v>161.8806609308659</v>
-      </c>
-      <c r="F325" t="n">
-        <v>108.48649397566</v>
+        <v>107.8029861923239</v>
       </c>
     </row>
     <row r="326">
@@ -6375,16 +4421,10 @@
         <v>1</v>
       </c>
       <c r="C326" t="n">
-        <v>139.0903057368079</v>
+        <v>173.6430086396139</v>
       </c>
       <c r="D326" t="n">
-        <v>165.3191730167398</v>
-      </c>
-      <c r="E326" t="n">
-        <v>175.9551937804434</v>
-      </c>
-      <c r="F326" t="n">
-        <v>161.7591181380299</v>
+        <v>159.6152055493196</v>
       </c>
     </row>
     <row r="327">
@@ -6393,16 +4433,10 @@
         <v>2</v>
       </c>
       <c r="C327" t="n">
-        <v>194.4752079422881</v>
+        <v>169.0225127163492</v>
       </c>
       <c r="D327" t="n">
-        <v>174.9494161050936</v>
-      </c>
-      <c r="E327" t="n">
-        <v>171.9744848090871</v>
-      </c>
-      <c r="F327" t="n">
-        <v>123.6514967895093</v>
+        <v>121.5421088972642</v>
       </c>
     </row>
     <row r="328">
@@ -6411,16 +4445,10 @@
         <v>3</v>
       </c>
       <c r="C328" t="n">
-        <v>235.3028722809917</v>
+        <v>212.2177643820679</v>
       </c>
       <c r="D328" t="n">
-        <v>170.6411494603037</v>
-      </c>
-      <c r="E328" t="n">
-        <v>216.2687609146228</v>
-      </c>
-      <c r="F328" t="n">
-        <v>147.0632927249308</v>
+        <v>144.9801117584005</v>
       </c>
     </row>
     <row r="329">
@@ -6429,16 +4457,10 @@
         <v>4</v>
       </c>
       <c r="C329" t="n">
-        <v>289.1851916748816</v>
+        <v>274.7444632392582</v>
       </c>
       <c r="D329" t="n">
-        <v>213.3759743105836</v>
-      </c>
-      <c r="E329" t="n">
-        <v>278.9165297744277</v>
-      </c>
-      <c r="F329" t="n">
-        <v>171.5565370477667</v>
+        <v>168.8026610026036</v>
       </c>
     </row>
     <row r="330">
@@ -6447,16 +4469,10 @@
         <v>5</v>
       </c>
       <c r="C330" t="n">
-        <v>246.062472054456</v>
+        <v>251.8938770068808</v>
       </c>
       <c r="D330" t="n">
-        <v>260.5830482731022</v>
-      </c>
-      <c r="E330" t="n">
-        <v>255.1689394207694</v>
-      </c>
-      <c r="F330" t="n">
-        <v>199.8427363425678</v>
+        <v>196.927469419916</v>
       </c>
     </row>
     <row r="331">
@@ -6465,16 +4481,10 @@
         <v>6</v>
       </c>
       <c r="C331" t="n">
-        <v>165.4883730885335</v>
+        <v>163.1750912400638</v>
       </c>
       <c r="D331" t="n">
-        <v>145.5236733351237</v>
-      </c>
-      <c r="E331" t="n">
-        <v>165.5464763618138</v>
-      </c>
-      <c r="F331" t="n">
-        <v>110.6027184596714</v>
+        <v>108.912780236606</v>
       </c>
     </row>
     <row r="332">
@@ -6483,16 +4493,10 @@
         <v>7</v>
       </c>
       <c r="C332" t="n">
-        <v>219.900343666559</v>
+        <v>225.2204456727346</v>
       </c>
       <c r="D332" t="n">
-        <v>210.9481819353684</v>
-      </c>
-      <c r="E332" t="n">
-        <v>228.6117600334613</v>
-      </c>
-      <c r="F332" t="n">
-        <v>175.212382405698</v>
+        <v>172.3453284740134</v>
       </c>
     </row>
     <row r="333">
@@ -6501,16 +4505,10 @@
         <v>8</v>
       </c>
       <c r="C333" t="n">
-        <v>137.3499285685456</v>
+        <v>172.3077542846736</v>
       </c>
       <c r="D333" t="n">
-        <v>130.5432951976845</v>
-      </c>
-      <c r="E333" t="n">
-        <v>175.066235340574</v>
-      </c>
-      <c r="F333" t="n">
-        <v>117.9149513254066</v>
+        <v>115.8420779726656</v>
       </c>
     </row>
     <row r="334">
@@ -6519,16 +4517,10 @@
         <v>9</v>
       </c>
       <c r="C334" t="n">
-        <v>249.6337891387286</v>
+        <v>178.1866334210403</v>
       </c>
       <c r="D334" t="n">
-        <v>162.3923344310637</v>
-      </c>
-      <c r="E334" t="n">
-        <v>181.9498233287657</v>
-      </c>
-      <c r="F334" t="n">
-        <v>128.8898227533397</v>
+        <v>126.839800289767</v>
       </c>
     </row>
     <row r="335">
@@ -6537,16 +4529,10 @@
         <v>10</v>
       </c>
       <c r="C335" t="n">
-        <v>241.2878912282384</v>
+        <v>227.7644273950749</v>
       </c>
       <c r="D335" t="n">
-        <v>226.7119727049951</v>
-      </c>
-      <c r="E335" t="n">
-        <v>230.7376888323819</v>
-      </c>
-      <c r="F335" t="n">
-        <v>186.7465496011185</v>
+        <v>184.326318513455</v>
       </c>
     </row>
     <row r="336">
@@ -6555,16 +4541,10 @@
         <v>11</v>
       </c>
       <c r="C336" t="n">
-        <v>316.6258542975037</v>
+        <v>248.0943253158871</v>
       </c>
       <c r="D336" t="n">
-        <v>304.9576977978696</v>
-      </c>
-      <c r="E336" t="n">
-        <v>252.5838987931249</v>
-      </c>
-      <c r="F336" t="n">
-        <v>260.9856880609016</v>
+        <v>256.5810103989737</v>
       </c>
     </row>
     <row r="337">
@@ -6573,16 +4553,10 @@
         <v>12</v>
       </c>
       <c r="C337" t="n">
-        <v>371.2605446135307</v>
+        <v>321.1133847608605</v>
       </c>
       <c r="D337" t="n">
-        <v>421.8963638707368</v>
-      </c>
-      <c r="E337" t="n">
-        <v>327.966444495823</v>
-      </c>
-      <c r="F337" t="n">
-        <v>353.4725980622735</v>
+        <v>349.5177902331895</v>
       </c>
     </row>
     <row r="338">
@@ -6593,16 +4567,10 @@
         <v>1</v>
       </c>
       <c r="C338" t="n">
-        <v>297.7964010221914</v>
+        <v>225.8251455034174</v>
       </c>
       <c r="D338" t="n">
-        <v>243.048992229881</v>
-      </c>
-      <c r="E338" t="n">
-        <v>231.0087538531504</v>
-      </c>
-      <c r="F338" t="n">
-        <v>190.6172203996057</v>
+        <v>187.7334818888509</v>
       </c>
     </row>
     <row r="339">
@@ -6611,16 +4579,10 @@
         <v>2</v>
       </c>
       <c r="C339" t="n">
-        <v>559.8862431235921</v>
+        <v>471.3822930830684</v>
       </c>
       <c r="D339" t="n">
-        <v>592.6303438986938</v>
-      </c>
-      <c r="E339" t="n">
-        <v>480.7066669626709</v>
-      </c>
-      <c r="F339" t="n">
-        <v>521.5353694448057</v>
+        <v>513.0223765920398</v>
       </c>
     </row>
     <row r="340">
@@ -6629,16 +4591,10 @@
         <v>3</v>
       </c>
       <c r="C340" t="n">
-        <v>614.6787813338988</v>
+        <v>446.4392972040919</v>
       </c>
       <c r="D340" t="n">
-        <v>553.1216543054476</v>
-      </c>
-      <c r="E340" t="n">
-        <v>455.8807203900582</v>
-      </c>
-      <c r="F340" t="n">
-        <v>486.5673058475199</v>
+        <v>478.316807318544</v>
       </c>
     </row>
     <row r="341">
@@ -6647,16 +4603,10 @@
         <v>4</v>
       </c>
       <c r="C341" t="n">
-        <v>537.5815507853677</v>
+        <v>386.3175176644331</v>
       </c>
       <c r="D341" t="n">
-        <v>433.3609389759198</v>
-      </c>
-      <c r="E341" t="n">
-        <v>391.8195499107002</v>
-      </c>
-      <c r="F341" t="n">
-        <v>344.9532554309451</v>
+        <v>340.2529332858516</v>
       </c>
     </row>
     <row r="342">
@@ -6665,16 +4615,10 @@
         <v>5</v>
       </c>
       <c r="C342" t="n">
-        <v>317.4652277915966</v>
+        <v>247.4442536236556</v>
       </c>
       <c r="D342" t="n">
-        <v>330.1797630292722</v>
-      </c>
-      <c r="E342" t="n">
-        <v>252.9734837536494</v>
-      </c>
-      <c r="F342" t="n">
-        <v>283.0428394725889</v>
+        <v>279.0408903879639</v>
       </c>
     </row>
     <row r="343">
@@ -6683,16 +4627,46 @@
         <v>6</v>
       </c>
       <c r="C343" t="n">
-        <v>303.5006163294281</v>
+        <v>257.5799685485886</v>
       </c>
       <c r="D343" t="n">
-        <v>272.856887503357</v>
-      </c>
-      <c r="E343" t="n">
-        <v>262.6227973397258</v>
-      </c>
-      <c r="F343" t="n">
-        <v>213.2435479152221</v>
+        <v>209.9590944786428</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="n"/>
+      <c r="B344" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C344" t="n">
+        <v>299.8538721202974</v>
+      </c>
+      <c r="D344" t="n">
+        <v>294.3014252818322</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="n"/>
+      <c r="B345" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C345" t="n">
+        <v>270.8776262820589</v>
+      </c>
+      <c r="D345" t="n">
+        <v>188.1816915657619</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="n"/>
+      <c r="B346" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C346" t="n">
+        <v>264.7707020902119</v>
+      </c>
+      <c r="D346" t="n">
+        <v>283.8991385116897</v>
       </c>
     </row>
   </sheetData>
@@ -6703,7 +4677,6 @@
     <mergeCell ref="A62:A73"/>
     <mergeCell ref="A278:A289"/>
     <mergeCell ref="A122:A133"/>
-    <mergeCell ref="A338:A343"/>
     <mergeCell ref="A38:A49"/>
     <mergeCell ref="A14:A25"/>
     <mergeCell ref="A230:A241"/>
@@ -6720,6 +4693,7 @@
     <mergeCell ref="A50:A61"/>
     <mergeCell ref="A146:A157"/>
     <mergeCell ref="A86:A97"/>
+    <mergeCell ref="A338:A346"/>
     <mergeCell ref="A158:A169"/>
     <mergeCell ref="A242:A253"/>
     <mergeCell ref="A254:A265"/>
